--- a/Behavioral_data.xlsx
+++ b/Behavioral_data.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="27628"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="28730"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\u_backup\近红外冥想项目\Study1\results\Revision\Social cognitive and affective neuroscience\Data and Code\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\u_backup\近红外冥想项目\Study1\results\Revision\Social cognitive and affective neuroscience\Final version\Data and Code\Intertemporal-Meditation-fNIRS\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{53146CDC-37E8-4420-B0E1-D88D3A5DD185}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5AEB38A2-1F39-441A-A446-8E4EE6C95BA5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-93" yWindow="-93" windowWidth="25786" windowHeight="13866" activeTab="1" xr2:uid="{EF8BB245-B73D-4BA7-AC74-DEBACD680290}"/>
+    <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="15675" xr2:uid="{EF8BB245-B73D-4BA7-AC74-DEBACD680290}"/>
   </bookViews>
   <sheets>
     <sheet name="Note" sheetId="7" r:id="rId1"/>
@@ -22,9 +22,9 @@
     <sheet name="viso_emo" sheetId="6" r:id="rId7"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">end!$A$1:$L$67</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">end!$A$1:$M$67</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">posttest!$A$1:$I$67</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">present!$A$1:$L$67</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">present!$A$1:$M$67</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">pretest!$A$1:$J$71</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1228" uniqueCount="104">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1364" uniqueCount="104">
   <si>
     <t>SubjectNo</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -829,16 +829,16 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{51086E2B-02D1-44BA-8E92-1943610C5BE0}">
-  <dimension ref="A1:D26"/>
-  <sheetFormatPr defaultRowHeight="14" x14ac:dyDescent="0.45"/>
+  <dimension ref="A1:D27"/>
+  <sheetFormatPr defaultRowHeight="13.9" x14ac:dyDescent="0.4"/>
   <cols>
-    <col min="1" max="1" width="19.46875" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="46.3515625" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="17.64453125" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="108.9375" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="19.46484375" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="46.33203125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="17.6640625" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="108.9296875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="1" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A1" s="6" t="s">
         <v>46</v>
       </c>
@@ -852,7 +852,7 @@
         <v>95</v>
       </c>
     </row>
-    <row r="2" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="2" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A2" s="7" t="s">
         <v>58</v>
       </c>
@@ -866,7 +866,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="3" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="3" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A3" s="7"/>
       <c r="B3" s="7" t="s">
         <v>98</v>
@@ -878,7 +878,7 @@
         <v>71</v>
       </c>
     </row>
-    <row r="4" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="4" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A4" s="7"/>
       <c r="B4" s="7"/>
       <c r="C4" s="7" t="s">
@@ -888,7 +888,7 @@
         <v>72</v>
       </c>
     </row>
-    <row r="5" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="5" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A5" s="7"/>
       <c r="B5" s="7"/>
       <c r="C5" s="7" t="s">
@@ -898,7 +898,7 @@
         <v>73</v>
       </c>
     </row>
-    <row r="6" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="6" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A6" s="7"/>
       <c r="B6" s="7"/>
       <c r="C6" s="7" t="s">
@@ -908,7 +908,7 @@
         <v>74</v>
       </c>
     </row>
-    <row r="7" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="7" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A7" s="7"/>
       <c r="B7" s="7"/>
       <c r="C7" s="7" t="s">
@@ -918,7 +918,7 @@
         <v>103</v>
       </c>
     </row>
-    <row r="8" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="8" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A8" s="7"/>
       <c r="B8" s="7"/>
       <c r="C8" s="7" t="s">
@@ -928,7 +928,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="9" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="9" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A9" s="7"/>
       <c r="B9" s="7"/>
       <c r="C9" s="7" t="s">
@@ -938,7 +938,7 @@
         <v>76</v>
       </c>
     </row>
-    <row r="10" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="10" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A10" s="7"/>
       <c r="B10" s="7"/>
       <c r="C10" s="7" t="s">
@@ -948,7 +948,7 @@
         <v>77</v>
       </c>
     </row>
-    <row r="11" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="11" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A11" s="7"/>
       <c r="B11" s="7"/>
       <c r="C11" s="7" t="s">
@@ -958,7 +958,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="12" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="12" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A12" s="7" t="s">
         <v>59</v>
       </c>
@@ -972,7 +972,7 @@
         <v>79</v>
       </c>
     </row>
-    <row r="13" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="13" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A13" s="7"/>
       <c r="B13" s="7" t="s">
         <v>100</v>
@@ -984,139 +984,149 @@
         <v>80</v>
       </c>
     </row>
-    <row r="14" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="14" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A14" s="7"/>
       <c r="B14" s="7"/>
       <c r="C14" s="7" t="s">
-        <v>62</v>
+        <v>50</v>
       </c>
       <c r="D14" s="7" t="s">
-        <v>81</v>
-      </c>
-    </row>
-    <row r="15" spans="1:4" x14ac:dyDescent="0.45">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="15" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A15" s="7"/>
       <c r="B15" s="7"/>
       <c r="C15" s="7" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="D15" s="7" t="s">
-        <v>82</v>
-      </c>
-    </row>
-    <row r="16" spans="1:4" x14ac:dyDescent="0.45">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="16" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A16" s="7"/>
       <c r="B16" s="7"/>
       <c r="C16" s="7" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="D16" s="7" t="s">
-        <v>83</v>
-      </c>
-    </row>
-    <row r="17" spans="1:4" x14ac:dyDescent="0.45">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="17" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A17" s="7"/>
       <c r="B17" s="7"/>
       <c r="C17" s="7" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="D17" s="7" t="s">
-        <v>84</v>
-      </c>
-    </row>
-    <row r="18" spans="1:4" x14ac:dyDescent="0.45">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="18" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A18" s="7"/>
       <c r="B18" s="7"/>
       <c r="C18" s="7" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="D18" s="7" t="s">
-        <v>85</v>
-      </c>
-    </row>
-    <row r="19" spans="1:4" x14ac:dyDescent="0.45">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="19" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A19" s="7"/>
       <c r="B19" s="7"/>
       <c r="C19" s="7" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="D19" s="7" t="s">
-        <v>86</v>
-      </c>
-    </row>
-    <row r="20" spans="1:4" x14ac:dyDescent="0.45">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="20" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A20" s="7"/>
       <c r="B20" s="7"/>
       <c r="C20" s="7" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="D20" s="7" t="s">
-        <v>87</v>
-      </c>
-    </row>
-    <row r="21" spans="1:4" x14ac:dyDescent="0.45">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="21" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A21" s="7"/>
       <c r="B21" s="7"/>
       <c r="C21" s="7" t="s">
+        <v>68</v>
+      </c>
+      <c r="D21" s="7" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="22" spans="1:4" x14ac:dyDescent="0.4">
+      <c r="A22" s="7"/>
+      <c r="B22" s="7"/>
+      <c r="C22" s="7" t="s">
         <v>69</v>
       </c>
-      <c r="D21" s="7" t="s">
+      <c r="D22" s="7" t="s">
         <v>88</v>
       </c>
     </row>
-    <row r="22" spans="1:4" x14ac:dyDescent="0.45">
-      <c r="A22" s="7" t="s">
+    <row r="23" spans="1:4" x14ac:dyDescent="0.4">
+      <c r="A23" s="7" t="s">
         <v>93</v>
       </c>
-      <c r="B22" s="7" t="s">
+      <c r="B23" s="7" t="s">
         <v>101</v>
       </c>
-      <c r="C22" s="7" t="s">
+      <c r="C23" s="7" t="s">
         <v>33</v>
       </c>
-      <c r="D22" s="7" t="s">
+      <c r="D23" s="7" t="s">
         <v>89</v>
       </c>
     </row>
-    <row r="23" spans="1:4" x14ac:dyDescent="0.45">
-      <c r="A23" s="7"/>
-      <c r="B23" s="7" t="s">
+    <row r="24" spans="1:4" x14ac:dyDescent="0.4">
+      <c r="A24" s="7"/>
+      <c r="B24" s="7" t="s">
         <v>102</v>
       </c>
-      <c r="C23" s="7" t="s">
+      <c r="C24" s="7" t="s">
         <v>39</v>
       </c>
-      <c r="D23" s="7" t="s">
+      <c r="D24" s="7" t="s">
         <v>94</v>
       </c>
     </row>
-    <row r="24" spans="1:4" x14ac:dyDescent="0.45">
-      <c r="A24" s="7"/>
-      <c r="B24" s="7"/>
-      <c r="C24" s="7" t="s">
-        <v>34</v>
-      </c>
-      <c r="D24" s="7" t="s">
-        <v>90</v>
-      </c>
-    </row>
-    <row r="25" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="25" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A25" s="7"/>
       <c r="B25" s="7"/>
       <c r="C25" s="7" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="D25" s="7" t="s">
-        <v>91</v>
-      </c>
-    </row>
-    <row r="26" spans="1:4" x14ac:dyDescent="0.45">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="26" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A26" s="7"/>
       <c r="B26" s="7"/>
       <c r="C26" s="7" t="s">
+        <v>35</v>
+      </c>
+      <c r="D26" s="7" t="s">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="27" spans="1:4" x14ac:dyDescent="0.4">
+      <c r="A27" s="7"/>
+      <c r="B27" s="7"/>
+      <c r="C27" s="7" t="s">
         <v>36</v>
       </c>
-      <c r="D26" s="7" t="s">
+      <c r="D27" s="7" t="s">
         <v>92</v>
       </c>
     </row>
@@ -1130,21 +1140,21 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:J71"/>
-  <sheetFormatPr defaultRowHeight="14" x14ac:dyDescent="0.45"/>
+  <sheetFormatPr defaultRowHeight="13.9" x14ac:dyDescent="0.4"/>
   <cols>
-    <col min="1" max="1" width="13.52734375" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="13.1171875" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="10.64453125" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="7.64453125" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="7.41015625" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="15.234375" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="12.234375" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="21.52734375" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="31.1171875" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="13.53125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="13.1328125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="10.6640625" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="7.6640625" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="7.3984375" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="15.19921875" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="12.19921875" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="21.53125" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="31.1328125" bestFit="1" customWidth="1"/>
     <col min="10" max="10" width="11" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:10" x14ac:dyDescent="0.45">
+    <row r="1" spans="1:10" x14ac:dyDescent="0.4">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1176,7 +1186,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="2" spans="1:10" x14ac:dyDescent="0.45">
+    <row r="2" spans="1:10" x14ac:dyDescent="0.4">
       <c r="A2" s="2">
         <v>1</v>
       </c>
@@ -1208,7 +1218,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="3" spans="1:10" x14ac:dyDescent="0.45">
+    <row r="3" spans="1:10" x14ac:dyDescent="0.4">
       <c r="A3" s="2">
         <v>2</v>
       </c>
@@ -1240,7 +1250,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="4" spans="1:10" x14ac:dyDescent="0.45">
+    <row r="4" spans="1:10" x14ac:dyDescent="0.4">
       <c r="A4" s="3">
         <v>4</v>
       </c>
@@ -1272,7 +1282,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="5" spans="1:10" x14ac:dyDescent="0.45">
+    <row r="5" spans="1:10" x14ac:dyDescent="0.4">
       <c r="A5" s="3">
         <v>5</v>
       </c>
@@ -1304,7 +1314,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="6" spans="1:10" x14ac:dyDescent="0.45">
+    <row r="6" spans="1:10" x14ac:dyDescent="0.4">
       <c r="A6" s="3">
         <v>6</v>
       </c>
@@ -1336,7 +1346,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="7" spans="1:10" x14ac:dyDescent="0.45">
+    <row r="7" spans="1:10" x14ac:dyDescent="0.4">
       <c r="A7" s="3">
         <v>7</v>
       </c>
@@ -1368,7 +1378,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="8" spans="1:10" x14ac:dyDescent="0.45">
+    <row r="8" spans="1:10" x14ac:dyDescent="0.4">
       <c r="A8" s="3">
         <v>8</v>
       </c>
@@ -1400,7 +1410,7 @@
         <v>76</v>
       </c>
     </row>
-    <row r="9" spans="1:10" x14ac:dyDescent="0.45">
+    <row r="9" spans="1:10" x14ac:dyDescent="0.4">
       <c r="A9" s="3">
         <v>9</v>
       </c>
@@ -1432,7 +1442,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="10" spans="1:10" x14ac:dyDescent="0.45">
+    <row r="10" spans="1:10" x14ac:dyDescent="0.4">
       <c r="A10" s="2">
         <v>10</v>
       </c>
@@ -1464,7 +1474,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="11" spans="1:10" x14ac:dyDescent="0.45">
+    <row r="11" spans="1:10" x14ac:dyDescent="0.4">
       <c r="A11" s="2">
         <v>11</v>
       </c>
@@ -1496,7 +1506,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="12" spans="1:10" x14ac:dyDescent="0.45">
+    <row r="12" spans="1:10" x14ac:dyDescent="0.4">
       <c r="A12" s="2">
         <v>12</v>
       </c>
@@ -1528,7 +1538,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="13" spans="1:10" x14ac:dyDescent="0.45">
+    <row r="13" spans="1:10" x14ac:dyDescent="0.4">
       <c r="A13" s="2">
         <v>13</v>
       </c>
@@ -1560,7 +1570,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="14" spans="1:10" x14ac:dyDescent="0.45">
+    <row r="14" spans="1:10" x14ac:dyDescent="0.4">
       <c r="A14" s="2">
         <v>14</v>
       </c>
@@ -1592,7 +1602,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="15" spans="1:10" x14ac:dyDescent="0.45">
+    <row r="15" spans="1:10" x14ac:dyDescent="0.4">
       <c r="A15" s="2">
         <v>15</v>
       </c>
@@ -1624,7 +1634,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="16" spans="1:10" x14ac:dyDescent="0.45">
+    <row r="16" spans="1:10" x14ac:dyDescent="0.4">
       <c r="A16" s="2">
         <v>16</v>
       </c>
@@ -1656,7 +1666,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="17" spans="1:10" x14ac:dyDescent="0.45">
+    <row r="17" spans="1:10" x14ac:dyDescent="0.4">
       <c r="A17" s="2">
         <v>17</v>
       </c>
@@ -1688,7 +1698,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="18" spans="1:10" x14ac:dyDescent="0.45">
+    <row r="18" spans="1:10" x14ac:dyDescent="0.4">
       <c r="A18" s="2">
         <v>18</v>
       </c>
@@ -1720,7 +1730,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="19" spans="1:10" x14ac:dyDescent="0.45">
+    <row r="19" spans="1:10" x14ac:dyDescent="0.4">
       <c r="A19" s="2">
         <v>19</v>
       </c>
@@ -1752,7 +1762,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="20" spans="1:10" x14ac:dyDescent="0.45">
+    <row r="20" spans="1:10" x14ac:dyDescent="0.4">
       <c r="A20" s="2">
         <v>20</v>
       </c>
@@ -1784,7 +1794,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="21" spans="1:10" x14ac:dyDescent="0.45">
+    <row r="21" spans="1:10" x14ac:dyDescent="0.4">
       <c r="A21" s="2">
         <v>21</v>
       </c>
@@ -1816,7 +1826,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="22" spans="1:10" x14ac:dyDescent="0.45">
+    <row r="22" spans="1:10" x14ac:dyDescent="0.4">
       <c r="A22" s="2">
         <v>22</v>
       </c>
@@ -1848,7 +1858,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="23" spans="1:10" x14ac:dyDescent="0.45">
+    <row r="23" spans="1:10" x14ac:dyDescent="0.4">
       <c r="A23" s="2">
         <v>23</v>
       </c>
@@ -1880,7 +1890,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="24" spans="1:10" x14ac:dyDescent="0.45">
+    <row r="24" spans="1:10" x14ac:dyDescent="0.4">
       <c r="A24" s="2">
         <v>24</v>
       </c>
@@ -1912,7 +1922,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="25" spans="1:10" x14ac:dyDescent="0.45">
+    <row r="25" spans="1:10" x14ac:dyDescent="0.4">
       <c r="A25" s="2">
         <v>25</v>
       </c>
@@ -1944,7 +1954,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="26" spans="1:10" x14ac:dyDescent="0.45">
+    <row r="26" spans="1:10" x14ac:dyDescent="0.4">
       <c r="A26" s="2">
         <v>26</v>
       </c>
@@ -1976,7 +1986,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="27" spans="1:10" x14ac:dyDescent="0.45">
+    <row r="27" spans="1:10" x14ac:dyDescent="0.4">
       <c r="A27" s="2">
         <v>27</v>
       </c>
@@ -2008,7 +2018,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="28" spans="1:10" x14ac:dyDescent="0.45">
+    <row r="28" spans="1:10" x14ac:dyDescent="0.4">
       <c r="A28" s="2">
         <v>29</v>
       </c>
@@ -2040,7 +2050,7 @@
         <v>89</v>
       </c>
     </row>
-    <row r="29" spans="1:10" x14ac:dyDescent="0.45">
+    <row r="29" spans="1:10" x14ac:dyDescent="0.4">
       <c r="A29" s="2">
         <v>30</v>
       </c>
@@ -2072,7 +2082,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="30" spans="1:10" x14ac:dyDescent="0.45">
+    <row r="30" spans="1:10" x14ac:dyDescent="0.4">
       <c r="A30" s="2">
         <v>31</v>
       </c>
@@ -2104,7 +2114,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="31" spans="1:10" x14ac:dyDescent="0.45">
+    <row r="31" spans="1:10" x14ac:dyDescent="0.4">
       <c r="A31" s="2">
         <v>32</v>
       </c>
@@ -2136,7 +2146,7 @@
         <v>95</v>
       </c>
     </row>
-    <row r="32" spans="1:10" x14ac:dyDescent="0.45">
+    <row r="32" spans="1:10" x14ac:dyDescent="0.4">
       <c r="A32" s="2">
         <v>33</v>
       </c>
@@ -2168,7 +2178,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="33" spans="1:10" x14ac:dyDescent="0.45">
+    <row r="33" spans="1:10" x14ac:dyDescent="0.4">
       <c r="A33" s="2">
         <v>34</v>
       </c>
@@ -2200,7 +2210,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="34" spans="1:10" x14ac:dyDescent="0.45">
+    <row r="34" spans="1:10" x14ac:dyDescent="0.4">
       <c r="A34" s="2">
         <v>35</v>
       </c>
@@ -2232,7 +2242,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="35" spans="1:10" x14ac:dyDescent="0.45">
+    <row r="35" spans="1:10" x14ac:dyDescent="0.4">
       <c r="A35" s="2">
         <v>36</v>
       </c>
@@ -2264,7 +2274,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="36" spans="1:10" x14ac:dyDescent="0.45">
+    <row r="36" spans="1:10" x14ac:dyDescent="0.4">
       <c r="A36" s="2">
         <v>37</v>
       </c>
@@ -2296,7 +2306,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="37" spans="1:10" x14ac:dyDescent="0.45">
+    <row r="37" spans="1:10" x14ac:dyDescent="0.4">
       <c r="A37" s="2">
         <v>38</v>
       </c>
@@ -2328,7 +2338,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="38" spans="1:10" x14ac:dyDescent="0.45">
+    <row r="38" spans="1:10" x14ac:dyDescent="0.4">
       <c r="A38" s="2">
         <v>39</v>
       </c>
@@ -2360,7 +2370,7 @@
         <v>71</v>
       </c>
     </row>
-    <row r="39" spans="1:10" x14ac:dyDescent="0.45">
+    <row r="39" spans="1:10" x14ac:dyDescent="0.4">
       <c r="A39" s="2">
         <v>40</v>
       </c>
@@ -2392,7 +2402,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="40" spans="1:10" x14ac:dyDescent="0.45">
+    <row r="40" spans="1:10" x14ac:dyDescent="0.4">
       <c r="A40" s="2">
         <v>41</v>
       </c>
@@ -2424,7 +2434,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="41" spans="1:10" x14ac:dyDescent="0.45">
+    <row r="41" spans="1:10" x14ac:dyDescent="0.4">
       <c r="A41" s="2">
         <v>42</v>
       </c>
@@ -2456,7 +2466,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="42" spans="1:10" x14ac:dyDescent="0.45">
+    <row r="42" spans="1:10" x14ac:dyDescent="0.4">
       <c r="A42" s="2">
         <v>43</v>
       </c>
@@ -2488,7 +2498,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="43" spans="1:10" x14ac:dyDescent="0.45">
+    <row r="43" spans="1:10" x14ac:dyDescent="0.4">
       <c r="A43" s="2">
         <v>44</v>
       </c>
@@ -2520,7 +2530,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="44" spans="1:10" x14ac:dyDescent="0.45">
+    <row r="44" spans="1:10" x14ac:dyDescent="0.4">
       <c r="A44" s="2">
         <v>45</v>
       </c>
@@ -2552,7 +2562,7 @@
         <v>55</v>
       </c>
     </row>
-    <row r="45" spans="1:10" x14ac:dyDescent="0.45">
+    <row r="45" spans="1:10" x14ac:dyDescent="0.4">
       <c r="A45" s="2">
         <v>46</v>
       </c>
@@ -2584,7 +2594,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="46" spans="1:10" x14ac:dyDescent="0.45">
+    <row r="46" spans="1:10" x14ac:dyDescent="0.4">
       <c r="A46" s="2">
         <v>47</v>
       </c>
@@ -2616,7 +2626,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="47" spans="1:10" x14ac:dyDescent="0.45">
+    <row r="47" spans="1:10" x14ac:dyDescent="0.4">
       <c r="A47" s="2">
         <v>48</v>
       </c>
@@ -2648,7 +2658,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="48" spans="1:10" x14ac:dyDescent="0.45">
+    <row r="48" spans="1:10" x14ac:dyDescent="0.4">
       <c r="A48" s="2">
         <v>49</v>
       </c>
@@ -2680,7 +2690,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="49" spans="1:10" x14ac:dyDescent="0.45">
+    <row r="49" spans="1:10" x14ac:dyDescent="0.4">
       <c r="A49" s="2">
         <v>50</v>
       </c>
@@ -2712,7 +2722,7 @@
         <v>63</v>
       </c>
     </row>
-    <row r="50" spans="1:10" x14ac:dyDescent="0.45">
+    <row r="50" spans="1:10" x14ac:dyDescent="0.4">
       <c r="A50" s="2">
         <v>51</v>
       </c>
@@ -2744,7 +2754,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="51" spans="1:10" x14ac:dyDescent="0.45">
+    <row r="51" spans="1:10" x14ac:dyDescent="0.4">
       <c r="A51" s="2">
         <v>52</v>
       </c>
@@ -2776,7 +2786,7 @@
         <v>49</v>
       </c>
     </row>
-    <row r="52" spans="1:10" x14ac:dyDescent="0.45">
+    <row r="52" spans="1:10" x14ac:dyDescent="0.4">
       <c r="A52" s="2">
         <v>53</v>
       </c>
@@ -2808,7 +2818,7 @@
         <v>55</v>
       </c>
     </row>
-    <row r="53" spans="1:10" x14ac:dyDescent="0.45">
+    <row r="53" spans="1:10" x14ac:dyDescent="0.4">
       <c r="A53" s="2">
         <v>54</v>
       </c>
@@ -2840,7 +2850,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="54" spans="1:10" x14ac:dyDescent="0.45">
+    <row r="54" spans="1:10" x14ac:dyDescent="0.4">
       <c r="A54" s="2">
         <v>55</v>
       </c>
@@ -2872,7 +2882,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="55" spans="1:10" x14ac:dyDescent="0.45">
+    <row r="55" spans="1:10" x14ac:dyDescent="0.4">
       <c r="A55" s="2">
         <v>56</v>
       </c>
@@ -2904,7 +2914,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="56" spans="1:10" x14ac:dyDescent="0.45">
+    <row r="56" spans="1:10" x14ac:dyDescent="0.4">
       <c r="A56" s="2">
         <v>57</v>
       </c>
@@ -2936,7 +2946,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="57" spans="1:10" x14ac:dyDescent="0.45">
+    <row r="57" spans="1:10" x14ac:dyDescent="0.4">
       <c r="A57" s="2">
         <v>58</v>
       </c>
@@ -2968,7 +2978,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="58" spans="1:10" x14ac:dyDescent="0.45">
+    <row r="58" spans="1:10" x14ac:dyDescent="0.4">
       <c r="A58" s="2">
         <v>59</v>
       </c>
@@ -3000,7 +3010,7 @@
         <v>68</v>
       </c>
     </row>
-    <row r="59" spans="1:10" x14ac:dyDescent="0.45">
+    <row r="59" spans="1:10" x14ac:dyDescent="0.4">
       <c r="A59" s="2">
         <v>60</v>
       </c>
@@ -3032,7 +3042,7 @@
         <v>65</v>
       </c>
     </row>
-    <row r="60" spans="1:10" x14ac:dyDescent="0.45">
+    <row r="60" spans="1:10" x14ac:dyDescent="0.4">
       <c r="A60" s="2">
         <v>61</v>
       </c>
@@ -3064,7 +3074,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="61" spans="1:10" x14ac:dyDescent="0.45">
+    <row r="61" spans="1:10" x14ac:dyDescent="0.4">
       <c r="A61" s="2">
         <v>62</v>
       </c>
@@ -3096,7 +3106,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="62" spans="1:10" x14ac:dyDescent="0.45">
+    <row r="62" spans="1:10" x14ac:dyDescent="0.4">
       <c r="A62" s="2">
         <v>63</v>
       </c>
@@ -3128,7 +3138,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="63" spans="1:10" x14ac:dyDescent="0.45">
+    <row r="63" spans="1:10" x14ac:dyDescent="0.4">
       <c r="A63" s="2">
         <v>64</v>
       </c>
@@ -3160,7 +3170,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="64" spans="1:10" x14ac:dyDescent="0.45">
+    <row r="64" spans="1:10" x14ac:dyDescent="0.4">
       <c r="A64" s="2">
         <v>65</v>
       </c>
@@ -3192,7 +3202,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="65" spans="1:10" x14ac:dyDescent="0.45">
+    <row r="65" spans="1:10" x14ac:dyDescent="0.4">
       <c r="A65" s="2">
         <v>66</v>
       </c>
@@ -3224,7 +3234,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="66" spans="1:10" x14ac:dyDescent="0.45">
+    <row r="66" spans="1:10" x14ac:dyDescent="0.4">
       <c r="A66" s="2">
         <v>67</v>
       </c>
@@ -3256,7 +3266,7 @@
         <v>77</v>
       </c>
     </row>
-    <row r="67" spans="1:10" x14ac:dyDescent="0.45">
+    <row r="67" spans="1:10" x14ac:dyDescent="0.4">
       <c r="A67" s="2">
         <v>68</v>
       </c>
@@ -3288,7 +3298,7 @@
         <v>52</v>
       </c>
     </row>
-    <row r="68" spans="1:10" x14ac:dyDescent="0.45">
+    <row r="68" spans="1:10" x14ac:dyDescent="0.4">
       <c r="A68" s="2">
         <v>69</v>
       </c>
@@ -3320,7 +3330,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="69" spans="1:10" x14ac:dyDescent="0.45">
+    <row r="69" spans="1:10" x14ac:dyDescent="0.4">
       <c r="A69" s="2">
         <v>70</v>
       </c>
@@ -3352,7 +3362,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="70" spans="1:10" x14ac:dyDescent="0.45">
+    <row r="70" spans="1:10" x14ac:dyDescent="0.4">
       <c r="A70" s="2">
         <v>71</v>
       </c>
@@ -3384,7 +3394,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="71" spans="1:10" x14ac:dyDescent="0.45">
+    <row r="71" spans="1:10" x14ac:dyDescent="0.4">
       <c r="A71" s="2">
         <v>72</v>
       </c>
@@ -3426,20 +3436,20 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4124C2C7-716A-4BCD-8495-978B2570DA14}">
   <dimension ref="A1:I67"/>
-  <sheetFormatPr defaultRowHeight="14" x14ac:dyDescent="0.45"/>
+  <sheetFormatPr defaultRowHeight="13.9" x14ac:dyDescent="0.4"/>
   <cols>
-    <col min="1" max="1" width="13.52734375" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="13.1171875" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="21.52734375" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="10.64453125" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="15.234375" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="21.52734375" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="7.64453125" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="7.41015625" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="8.3515625" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="13.53125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="13.1328125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="21.53125" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="10.6640625" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="15.19921875" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="21.53125" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="7.6640625" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="7.3984375" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="8.33203125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="1" spans="1:9" x14ac:dyDescent="0.4">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -3468,7 +3478,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="2" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="2" spans="1:9" x14ac:dyDescent="0.4">
       <c r="A2" s="3">
         <v>4</v>
       </c>
@@ -3498,7 +3508,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="3" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="3" spans="1:9" x14ac:dyDescent="0.4">
       <c r="A3" s="3">
         <v>5</v>
       </c>
@@ -3528,7 +3538,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="4" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="4" spans="1:9" x14ac:dyDescent="0.4">
       <c r="A4" s="3">
         <v>6</v>
       </c>
@@ -3558,7 +3568,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="5" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="5" spans="1:9" x14ac:dyDescent="0.4">
       <c r="A5" s="3">
         <v>7</v>
       </c>
@@ -3588,7 +3598,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="6" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="6" spans="1:9" x14ac:dyDescent="0.4">
       <c r="A6" s="2">
         <v>10</v>
       </c>
@@ -3618,7 +3628,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="7" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="7" spans="1:9" x14ac:dyDescent="0.4">
       <c r="A7" s="2">
         <v>11</v>
       </c>
@@ -3648,7 +3658,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="8" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="8" spans="1:9" x14ac:dyDescent="0.4">
       <c r="A8" s="2">
         <v>12</v>
       </c>
@@ -3678,7 +3688,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="9" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="9" spans="1:9" x14ac:dyDescent="0.4">
       <c r="A9" s="2">
         <v>13</v>
       </c>
@@ -3708,7 +3718,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="10" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="10" spans="1:9" x14ac:dyDescent="0.4">
       <c r="A10" s="2">
         <v>14</v>
       </c>
@@ -3738,7 +3748,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="11" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="11" spans="1:9" x14ac:dyDescent="0.4">
       <c r="A11" s="2">
         <v>15</v>
       </c>
@@ -3768,7 +3778,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="12" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="12" spans="1:9" x14ac:dyDescent="0.4">
       <c r="A12" s="2">
         <v>16</v>
       </c>
@@ -3798,7 +3808,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="13" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="13" spans="1:9" x14ac:dyDescent="0.4">
       <c r="A13" s="2">
         <v>17</v>
       </c>
@@ -3828,7 +3838,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="14" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="14" spans="1:9" x14ac:dyDescent="0.4">
       <c r="A14" s="2">
         <v>18</v>
       </c>
@@ -3858,7 +3868,7 @@
         <v>90</v>
       </c>
     </row>
-    <row r="15" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="15" spans="1:9" x14ac:dyDescent="0.4">
       <c r="A15" s="2">
         <v>19</v>
       </c>
@@ -3888,7 +3898,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="16" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="16" spans="1:9" x14ac:dyDescent="0.4">
       <c r="A16" s="2">
         <v>20</v>
       </c>
@@ -3918,7 +3928,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="17" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="17" spans="1:9" x14ac:dyDescent="0.4">
       <c r="A17" s="2">
         <v>21</v>
       </c>
@@ -3948,7 +3958,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="18" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="18" spans="1:9" x14ac:dyDescent="0.4">
       <c r="A18" s="2">
         <v>22</v>
       </c>
@@ -3978,7 +3988,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="19" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="19" spans="1:9" x14ac:dyDescent="0.4">
       <c r="A19" s="2">
         <v>23</v>
       </c>
@@ -4008,7 +4018,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="20" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="20" spans="1:9" x14ac:dyDescent="0.4">
       <c r="A20" s="2">
         <v>24</v>
       </c>
@@ -4038,7 +4048,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="21" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="21" spans="1:9" x14ac:dyDescent="0.4">
       <c r="A21" s="2">
         <v>25</v>
       </c>
@@ -4068,7 +4078,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="22" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="22" spans="1:9" x14ac:dyDescent="0.4">
       <c r="A22" s="2">
         <v>26</v>
       </c>
@@ -4098,7 +4108,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="23" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="23" spans="1:9" x14ac:dyDescent="0.4">
       <c r="A23" s="2">
         <v>27</v>
       </c>
@@ -4128,7 +4138,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="24" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="24" spans="1:9" x14ac:dyDescent="0.4">
       <c r="A24" s="2">
         <v>29</v>
       </c>
@@ -4158,7 +4168,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="25" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="25" spans="1:9" x14ac:dyDescent="0.4">
       <c r="A25" s="2">
         <v>30</v>
       </c>
@@ -4188,7 +4198,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="26" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="26" spans="1:9" x14ac:dyDescent="0.4">
       <c r="A26" s="2">
         <v>31</v>
       </c>
@@ -4218,7 +4228,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="27" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="27" spans="1:9" x14ac:dyDescent="0.4">
       <c r="A27" s="2">
         <v>32</v>
       </c>
@@ -4248,7 +4258,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="28" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="28" spans="1:9" x14ac:dyDescent="0.4">
       <c r="A28" s="2">
         <v>33</v>
       </c>
@@ -4278,7 +4288,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="29" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="29" spans="1:9" x14ac:dyDescent="0.4">
       <c r="A29" s="2">
         <v>34</v>
       </c>
@@ -4308,7 +4318,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="30" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="30" spans="1:9" x14ac:dyDescent="0.4">
       <c r="A30" s="2">
         <v>35</v>
       </c>
@@ -4338,7 +4348,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="31" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="31" spans="1:9" x14ac:dyDescent="0.4">
       <c r="A31" s="2">
         <v>36</v>
       </c>
@@ -4368,7 +4378,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="32" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="32" spans="1:9" x14ac:dyDescent="0.4">
       <c r="A32" s="2">
         <v>37</v>
       </c>
@@ -4398,7 +4408,7 @@
         <v>90</v>
       </c>
     </row>
-    <row r="33" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="33" spans="1:9" x14ac:dyDescent="0.4">
       <c r="A33" s="2">
         <v>38</v>
       </c>
@@ -4428,7 +4438,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="34" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="34" spans="1:9" x14ac:dyDescent="0.4">
       <c r="A34" s="2">
         <v>39</v>
       </c>
@@ -4458,7 +4468,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="35" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="35" spans="1:9" x14ac:dyDescent="0.4">
       <c r="A35" s="2">
         <v>40</v>
       </c>
@@ -4488,7 +4498,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="36" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="36" spans="1:9" x14ac:dyDescent="0.4">
       <c r="A36" s="2">
         <v>41</v>
       </c>
@@ -4518,7 +4528,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="37" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="37" spans="1:9" x14ac:dyDescent="0.4">
       <c r="A37" s="2">
         <v>42</v>
       </c>
@@ -4548,7 +4558,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="38" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="38" spans="1:9" x14ac:dyDescent="0.4">
       <c r="A38" s="2">
         <v>43</v>
       </c>
@@ -4578,7 +4588,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="39" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="39" spans="1:9" x14ac:dyDescent="0.4">
       <c r="A39" s="2">
         <v>44</v>
       </c>
@@ -4608,7 +4618,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="40" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="40" spans="1:9" x14ac:dyDescent="0.4">
       <c r="A40" s="2">
         <v>45</v>
       </c>
@@ -4638,7 +4648,7 @@
         <v>90</v>
       </c>
     </row>
-    <row r="41" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="41" spans="1:9" x14ac:dyDescent="0.4">
       <c r="A41" s="2">
         <v>46</v>
       </c>
@@ -4668,7 +4678,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="42" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="42" spans="1:9" x14ac:dyDescent="0.4">
       <c r="A42" s="2">
         <v>47</v>
       </c>
@@ -4698,7 +4708,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="43" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="43" spans="1:9" x14ac:dyDescent="0.4">
       <c r="A43" s="2">
         <v>48</v>
       </c>
@@ -4728,7 +4738,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="44" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="44" spans="1:9" x14ac:dyDescent="0.4">
       <c r="A44" s="2">
         <v>49</v>
       </c>
@@ -4758,7 +4768,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="45" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="45" spans="1:9" x14ac:dyDescent="0.4">
       <c r="A45" s="2">
         <v>50</v>
       </c>
@@ -4788,7 +4798,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="46" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="46" spans="1:9" x14ac:dyDescent="0.4">
       <c r="A46" s="2">
         <v>51</v>
       </c>
@@ -4818,7 +4828,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="47" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="47" spans="1:9" x14ac:dyDescent="0.4">
       <c r="A47" s="2">
         <v>52</v>
       </c>
@@ -4848,7 +4858,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="48" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="48" spans="1:9" x14ac:dyDescent="0.4">
       <c r="A48" s="2">
         <v>53</v>
       </c>
@@ -4878,7 +4888,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="49" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="49" spans="1:9" x14ac:dyDescent="0.4">
       <c r="A49" s="2">
         <v>54</v>
       </c>
@@ -4908,7 +4918,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="50" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="50" spans="1:9" x14ac:dyDescent="0.4">
       <c r="A50" s="2">
         <v>55</v>
       </c>
@@ -4938,7 +4948,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="51" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="51" spans="1:9" x14ac:dyDescent="0.4">
       <c r="A51" s="2">
         <v>56</v>
       </c>
@@ -4968,7 +4978,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="52" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="52" spans="1:9" x14ac:dyDescent="0.4">
       <c r="A52" s="2">
         <v>57</v>
       </c>
@@ -4998,7 +5008,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="53" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="53" spans="1:9" x14ac:dyDescent="0.4">
       <c r="A53" s="2">
         <v>58</v>
       </c>
@@ -5028,7 +5038,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="54" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="54" spans="1:9" x14ac:dyDescent="0.4">
       <c r="A54" s="2">
         <v>59</v>
       </c>
@@ -5058,7 +5068,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="55" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="55" spans="1:9" x14ac:dyDescent="0.4">
       <c r="A55" s="2">
         <v>60</v>
       </c>
@@ -5088,7 +5098,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="56" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="56" spans="1:9" x14ac:dyDescent="0.4">
       <c r="A56" s="2">
         <v>61</v>
       </c>
@@ -5118,7 +5128,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="57" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="57" spans="1:9" x14ac:dyDescent="0.4">
       <c r="A57" s="2">
         <v>62</v>
       </c>
@@ -5148,7 +5158,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="58" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="58" spans="1:9" x14ac:dyDescent="0.4">
       <c r="A58" s="2">
         <v>63</v>
       </c>
@@ -5178,7 +5188,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="59" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="59" spans="1:9" x14ac:dyDescent="0.4">
       <c r="A59" s="2">
         <v>64</v>
       </c>
@@ -5208,7 +5218,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="60" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="60" spans="1:9" x14ac:dyDescent="0.4">
       <c r="A60" s="2">
         <v>65</v>
       </c>
@@ -5238,7 +5248,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="61" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="61" spans="1:9" x14ac:dyDescent="0.4">
       <c r="A61" s="2">
         <v>66</v>
       </c>
@@ -5268,7 +5278,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="62" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="62" spans="1:9" x14ac:dyDescent="0.4">
       <c r="A62" s="2">
         <v>67</v>
       </c>
@@ -5298,7 +5308,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="63" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="63" spans="1:9" x14ac:dyDescent="0.4">
       <c r="A63" s="2">
         <v>68</v>
       </c>
@@ -5328,7 +5338,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="64" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="64" spans="1:9" x14ac:dyDescent="0.4">
       <c r="A64" s="2">
         <v>69</v>
       </c>
@@ -5358,7 +5368,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="65" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="65" spans="1:9" x14ac:dyDescent="0.4">
       <c r="A65" s="2">
         <v>70</v>
       </c>
@@ -5388,7 +5398,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="66" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="66" spans="1:9" x14ac:dyDescent="0.4">
       <c r="A66" s="2">
         <v>71</v>
       </c>
@@ -5418,7 +5428,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="67" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="67" spans="1:9" x14ac:dyDescent="0.4">
       <c r="A67" s="2">
         <v>72</v>
       </c>
@@ -5457,20 +5467,21 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{26FAC1FF-5E09-4135-A43D-31190E34F3D4}">
-  <dimension ref="A1:L67"/>
-  <sheetFormatPr defaultRowHeight="14" x14ac:dyDescent="0.45"/>
+  <dimension ref="A1:M67"/>
+  <sheetFormatPr defaultRowHeight="13.9" x14ac:dyDescent="0.4"/>
   <cols>
-    <col min="1" max="1" width="13.52734375" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="13.1171875" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="13.87890625" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="15.52734375" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="15.64453125" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="11.234375" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="6.76171875" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="7.64453125" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="13.53125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="13.1328125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="10.6640625" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="13.86328125" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="15.53125" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="15.6640625" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="11.19921875" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="6.73046875" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="7.6640625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:12" x14ac:dyDescent="0.45">
+    <row r="1" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -5478,37 +5489,40 @@
         <v>30</v>
       </c>
       <c r="C1" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="D1" s="1" t="s">
+      <c r="E1" s="1" t="s">
         <v>29</v>
       </c>
-      <c r="E1" s="1" t="s">
-        <v>20</v>
-      </c>
       <c r="F1" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="G1" s="1" t="s">
         <v>21</v>
       </c>
-      <c r="G1" s="1" t="s">
+      <c r="H1" s="1" t="s">
         <v>22</v>
       </c>
-      <c r="H1" s="1" t="s">
+      <c r="I1" s="1" t="s">
         <v>23</v>
       </c>
-      <c r="I1" s="1" t="s">
+      <c r="J1" s="1" t="s">
         <v>24</v>
       </c>
-      <c r="J1" s="1" t="s">
+      <c r="K1" s="1" t="s">
         <v>25</v>
       </c>
-      <c r="K1" s="1" t="s">
+      <c r="L1" s="1" t="s">
         <v>26</v>
       </c>
-      <c r="L1" s="1" t="s">
+      <c r="M1" s="1" t="s">
         <v>27</v>
       </c>
     </row>
-    <row r="2" spans="1:12" x14ac:dyDescent="0.45">
+    <row r="2" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A2" s="3">
         <v>4</v>
       </c>
@@ -5516,37 +5530,40 @@
         <v>31</v>
       </c>
       <c r="C2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="D2" t="s">
-        <v>18</v>
-      </c>
-      <c r="E2">
-        <v>50</v>
+        <v>13</v>
+      </c>
+      <c r="E2" t="s">
+        <v>18</v>
       </c>
       <c r="F2">
-        <v>20</v>
+        <v>50</v>
       </c>
       <c r="G2">
-        <v>60</v>
+        <v>20</v>
       </c>
       <c r="H2">
-        <v>20</v>
+        <v>60</v>
       </c>
       <c r="I2">
         <v>20</v>
       </c>
       <c r="J2">
+        <v>20</v>
+      </c>
+      <c r="K2">
         <v>10</v>
       </c>
-      <c r="K2">
-        <v>20</v>
-      </c>
       <c r="L2">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="3" spans="1:12" x14ac:dyDescent="0.45">
+        <v>20</v>
+      </c>
+      <c r="M2">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="3" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A3" s="3">
         <v>5</v>
       </c>
@@ -5554,37 +5571,40 @@
         <v>31</v>
       </c>
       <c r="C3" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="D3" t="s">
-        <v>18</v>
-      </c>
-      <c r="E3">
+        <v>13</v>
+      </c>
+      <c r="E3" t="s">
+        <v>18</v>
+      </c>
+      <c r="F3">
         <v>90</v>
       </c>
-      <c r="F3">
-        <v>60</v>
-      </c>
       <c r="G3">
-        <v>50</v>
+        <v>60</v>
       </c>
       <c r="H3">
+        <v>50</v>
+      </c>
+      <c r="I3">
         <v>10</v>
       </c>
-      <c r="I3">
+      <c r="J3">
         <v>70</v>
-      </c>
-      <c r="J3">
-        <v>10</v>
       </c>
       <c r="K3">
         <v>10</v>
       </c>
       <c r="L3">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="4" spans="1:12" x14ac:dyDescent="0.45">
+        <v>10</v>
+      </c>
+      <c r="M3">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="4" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A4" s="3">
         <v>6</v>
       </c>
@@ -5595,34 +5615,37 @@
         <v>13</v>
       </c>
       <c r="D4" t="s">
-        <v>18</v>
-      </c>
-      <c r="E4">
-        <v>50</v>
+        <v>13</v>
+      </c>
+      <c r="E4" t="s">
+        <v>18</v>
       </c>
       <c r="F4">
-        <v>20</v>
+        <v>50</v>
       </c>
       <c r="G4">
-        <v>50</v>
+        <v>20</v>
       </c>
       <c r="H4">
+        <v>50</v>
+      </c>
+      <c r="I4">
         <v>10</v>
       </c>
-      <c r="I4">
-        <v>50</v>
-      </c>
       <c r="J4">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="K4">
         <v>10</v>
       </c>
       <c r="L4">
-        <v>50</v>
-      </c>
-    </row>
-    <row r="5" spans="1:12" x14ac:dyDescent="0.45">
+        <v>10</v>
+      </c>
+      <c r="M4">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="5" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A5" s="3">
         <v>7</v>
       </c>
@@ -5633,34 +5656,37 @@
         <v>13</v>
       </c>
       <c r="D5" t="s">
-        <v>18</v>
-      </c>
-      <c r="E5">
+        <v>13</v>
+      </c>
+      <c r="E5" t="s">
+        <v>18</v>
+      </c>
+      <c r="F5">
         <v>80</v>
       </c>
-      <c r="F5">
+      <c r="G5">
         <v>25</v>
       </c>
-      <c r="G5">
+      <c r="H5">
         <v>70</v>
       </c>
-      <c r="H5">
-        <v>20</v>
-      </c>
       <c r="I5">
+        <v>20</v>
+      </c>
+      <c r="J5">
         <v>30</v>
       </c>
-      <c r="J5">
+      <c r="K5">
         <v>3</v>
       </c>
-      <c r="K5">
+      <c r="L5">
         <v>5</v>
       </c>
-      <c r="L5">
+      <c r="M5">
         <v>70</v>
       </c>
     </row>
-    <row r="6" spans="1:12" x14ac:dyDescent="0.45">
+    <row r="6" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A6" s="2">
         <v>10</v>
       </c>
@@ -5671,34 +5697,37 @@
         <v>13</v>
       </c>
       <c r="D6" t="s">
-        <v>18</v>
-      </c>
-      <c r="E6">
+        <v>13</v>
+      </c>
+      <c r="E6" t="s">
+        <v>18</v>
+      </c>
+      <c r="F6">
         <v>4</v>
       </c>
-      <c r="F6">
+      <c r="G6">
         <v>6</v>
       </c>
-      <c r="G6">
+      <c r="H6">
         <v>3</v>
-      </c>
-      <c r="H6">
-        <v>5</v>
       </c>
       <c r="I6">
         <v>5</v>
       </c>
       <c r="J6">
+        <v>5</v>
+      </c>
+      <c r="K6">
         <v>4</v>
       </c>
-      <c r="K6">
+      <c r="L6">
         <v>8</v>
       </c>
-      <c r="L6">
+      <c r="M6">
         <v>2</v>
       </c>
     </row>
-    <row r="7" spans="1:12" x14ac:dyDescent="0.45">
+    <row r="7" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A7" s="2">
         <v>11</v>
       </c>
@@ -5709,31 +5738,34 @@
         <v>13</v>
       </c>
       <c r="D7" t="s">
-        <v>18</v>
-      </c>
-      <c r="E7">
+        <v>13</v>
+      </c>
+      <c r="E7" t="s">
+        <v>18</v>
+      </c>
+      <c r="F7">
         <v>90</v>
       </c>
-      <c r="F7">
-        <v>1</v>
-      </c>
       <c r="G7">
+        <v>1</v>
+      </c>
+      <c r="H7">
         <v>99</v>
       </c>
-      <c r="I7">
+      <c r="J7">
         <v>2</v>
       </c>
-      <c r="J7">
-        <v>1</v>
-      </c>
       <c r="K7">
+        <v>1</v>
+      </c>
+      <c r="L7">
         <v>21</v>
       </c>
-      <c r="L7">
+      <c r="M7">
         <v>90</v>
       </c>
     </row>
-    <row r="8" spans="1:12" x14ac:dyDescent="0.45">
+    <row r="8" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A8" s="2">
         <v>12</v>
       </c>
@@ -5744,34 +5776,37 @@
         <v>13</v>
       </c>
       <c r="D8" t="s">
-        <v>18</v>
-      </c>
-      <c r="E8">
+        <v>13</v>
+      </c>
+      <c r="E8" t="s">
+        <v>18</v>
+      </c>
+      <c r="F8">
         <v>85</v>
       </c>
-      <c r="F8">
+      <c r="G8">
         <v>25</v>
       </c>
-      <c r="G8">
+      <c r="H8">
         <v>95</v>
       </c>
-      <c r="H8">
-        <v>1</v>
-      </c>
       <c r="I8">
+        <v>1</v>
+      </c>
+      <c r="J8">
         <v>90</v>
       </c>
-      <c r="J8">
-        <v>1</v>
-      </c>
       <c r="K8">
         <v>1</v>
       </c>
       <c r="L8">
+        <v>1</v>
+      </c>
+      <c r="M8">
         <v>98</v>
       </c>
     </row>
-    <row r="9" spans="1:12" x14ac:dyDescent="0.45">
+    <row r="9" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A9" s="2">
         <v>13</v>
       </c>
@@ -5782,34 +5817,37 @@
         <v>13</v>
       </c>
       <c r="D9" t="s">
-        <v>18</v>
-      </c>
-      <c r="E9">
+        <v>13</v>
+      </c>
+      <c r="E9" t="s">
+        <v>18</v>
+      </c>
+      <c r="F9">
         <v>70</v>
       </c>
-      <c r="F9">
-        <v>20</v>
-      </c>
       <c r="G9">
+        <v>20</v>
+      </c>
+      <c r="H9">
         <v>70</v>
       </c>
-      <c r="H9">
-        <v>60</v>
-      </c>
       <c r="I9">
+        <v>60</v>
+      </c>
+      <c r="J9">
         <v>30</v>
       </c>
-      <c r="J9">
-        <v>50</v>
-      </c>
       <c r="K9">
-        <v>60</v>
+        <v>50</v>
       </c>
       <c r="L9">
-        <v>50</v>
-      </c>
-    </row>
-    <row r="10" spans="1:12" x14ac:dyDescent="0.45">
+        <v>60</v>
+      </c>
+      <c r="M9">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="10" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A10" s="2">
         <v>14</v>
       </c>
@@ -5820,34 +5858,37 @@
         <v>13</v>
       </c>
       <c r="D10" t="s">
-        <v>18</v>
-      </c>
-      <c r="E10">
+        <v>13</v>
+      </c>
+      <c r="E10" t="s">
+        <v>18</v>
+      </c>
+      <c r="F10">
         <v>90</v>
       </c>
-      <c r="F10">
+      <c r="G10">
         <v>10</v>
       </c>
-      <c r="G10">
+      <c r="H10">
         <v>85</v>
       </c>
-      <c r="H10">
+      <c r="I10">
         <v>5</v>
       </c>
-      <c r="I10">
+      <c r="J10">
         <v>30</v>
       </c>
-      <c r="J10">
-        <v>1</v>
-      </c>
       <c r="K10">
         <v>1</v>
       </c>
       <c r="L10">
+        <v>1</v>
+      </c>
+      <c r="M10">
         <v>80</v>
       </c>
     </row>
-    <row r="11" spans="1:12" x14ac:dyDescent="0.45">
+    <row r="11" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A11" s="2">
         <v>15</v>
       </c>
@@ -5858,34 +5899,37 @@
         <v>13</v>
       </c>
       <c r="D11" t="s">
-        <v>18</v>
-      </c>
-      <c r="E11">
+        <v>13</v>
+      </c>
+      <c r="E11" t="s">
+        <v>18</v>
+      </c>
+      <c r="F11">
         <v>70</v>
       </c>
-      <c r="F11">
+      <c r="G11">
         <v>10</v>
       </c>
-      <c r="G11">
-        <v>60</v>
-      </c>
       <c r="H11">
+        <v>60</v>
+      </c>
+      <c r="I11">
         <v>40</v>
       </c>
-      <c r="I11">
+      <c r="J11">
         <v>30</v>
       </c>
-      <c r="J11">
-        <v>1</v>
-      </c>
       <c r="K11">
-        <v>20</v>
+        <v>1</v>
       </c>
       <c r="L11">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="12" spans="1:12" x14ac:dyDescent="0.45">
+        <v>20</v>
+      </c>
+      <c r="M11">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="12" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A12" s="2">
         <v>16</v>
       </c>
@@ -5896,31 +5940,34 @@
         <v>13</v>
       </c>
       <c r="D12" t="s">
-        <v>18</v>
-      </c>
-      <c r="E12">
-        <v>60</v>
+        <v>13</v>
+      </c>
+      <c r="E12" t="s">
+        <v>18</v>
       </c>
       <c r="F12">
+        <v>60</v>
+      </c>
+      <c r="G12">
         <v>10</v>
       </c>
-      <c r="G12">
+      <c r="H12">
         <v>30</v>
       </c>
-      <c r="H12">
-        <v>60</v>
-      </c>
       <c r="I12">
+        <v>60</v>
+      </c>
+      <c r="J12">
         <v>5</v>
       </c>
-      <c r="J12">
-        <v>60</v>
-      </c>
       <c r="K12">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="13" spans="1:12" x14ac:dyDescent="0.45">
+        <v>60</v>
+      </c>
+      <c r="L12">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="13" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A13" s="2">
         <v>17</v>
       </c>
@@ -5931,34 +5978,37 @@
         <v>13</v>
       </c>
       <c r="D13" t="s">
-        <v>18</v>
-      </c>
-      <c r="E13">
+        <v>13</v>
+      </c>
+      <c r="E13" t="s">
+        <v>18</v>
+      </c>
+      <c r="F13">
         <v>70</v>
       </c>
-      <c r="F13">
-        <v>20</v>
-      </c>
       <c r="G13">
+        <v>20</v>
+      </c>
+      <c r="H13">
         <v>80</v>
       </c>
-      <c r="H13">
-        <v>1</v>
-      </c>
       <c r="I13">
+        <v>1</v>
+      </c>
+      <c r="J13">
         <v>80</v>
       </c>
-      <c r="J13">
-        <v>1</v>
-      </c>
       <c r="K13">
         <v>1</v>
       </c>
       <c r="L13">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="14" spans="1:12" x14ac:dyDescent="0.45">
+        <v>1</v>
+      </c>
+      <c r="M13">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="14" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A14" s="2">
         <v>18</v>
       </c>
@@ -5969,25 +6019,25 @@
         <v>13</v>
       </c>
       <c r="D14" t="s">
-        <v>18</v>
-      </c>
-      <c r="E14">
-        <v>50</v>
+        <v>13</v>
+      </c>
+      <c r="E14" t="s">
+        <v>18</v>
       </c>
       <c r="F14">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="G14">
         <v>10</v>
       </c>
       <c r="H14">
-        <v>60</v>
+        <v>10</v>
       </c>
       <c r="I14">
-        <v>20</v>
+        <v>60</v>
       </c>
       <c r="J14">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="K14">
         <v>10</v>
@@ -5995,8 +6045,11 @@
       <c r="L14">
         <v>10</v>
       </c>
-    </row>
-    <row r="15" spans="1:12" x14ac:dyDescent="0.45">
+      <c r="M14">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="15" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A15" s="2">
         <v>19</v>
       </c>
@@ -6007,34 +6060,37 @@
         <v>13</v>
       </c>
       <c r="D15" t="s">
-        <v>18</v>
-      </c>
-      <c r="E15">
-        <v>50</v>
+        <v>13</v>
+      </c>
+      <c r="E15" t="s">
+        <v>18</v>
       </c>
       <c r="F15">
+        <v>50</v>
+      </c>
+      <c r="G15">
         <v>30</v>
       </c>
-      <c r="G15">
+      <c r="H15">
         <v>40</v>
       </c>
-      <c r="H15">
-        <v>60</v>
-      </c>
       <c r="I15">
+        <v>60</v>
+      </c>
+      <c r="J15">
         <v>40</v>
       </c>
-      <c r="J15">
-        <v>60</v>
-      </c>
       <c r="K15">
-        <v>50</v>
+        <v>60</v>
       </c>
       <c r="L15">
+        <v>50</v>
+      </c>
+      <c r="M15">
         <v>40</v>
       </c>
     </row>
-    <row r="16" spans="1:12" x14ac:dyDescent="0.45">
+    <row r="16" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A16" s="2">
         <v>20</v>
       </c>
@@ -6042,37 +6098,40 @@
         <v>31</v>
       </c>
       <c r="C16" t="s">
+        <v>14</v>
+      </c>
+      <c r="D16" t="s">
         <v>28</v>
       </c>
-      <c r="D16" t="s">
-        <v>18</v>
-      </c>
-      <c r="E16">
-        <v>50</v>
+      <c r="E16" t="s">
+        <v>18</v>
       </c>
       <c r="F16">
+        <v>50</v>
+      </c>
+      <c r="G16">
         <v>40</v>
       </c>
-      <c r="G16">
-        <v>60</v>
-      </c>
       <c r="H16">
+        <v>60</v>
+      </c>
+      <c r="I16">
         <v>40</v>
       </c>
-      <c r="I16">
-        <v>60</v>
-      </c>
       <c r="J16">
-        <v>20</v>
+        <v>60</v>
       </c>
       <c r="K16">
+        <v>20</v>
+      </c>
+      <c r="L16">
         <v>30</v>
       </c>
-      <c r="L16">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="17" spans="1:12" x14ac:dyDescent="0.45">
+      <c r="M16">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="17" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A17" s="2">
         <v>21</v>
       </c>
@@ -6083,34 +6142,37 @@
         <v>13</v>
       </c>
       <c r="D17" t="s">
-        <v>18</v>
-      </c>
-      <c r="E17">
+        <v>13</v>
+      </c>
+      <c r="E17" t="s">
+        <v>18</v>
+      </c>
+      <c r="F17">
         <v>79</v>
       </c>
-      <c r="F17">
-        <v>20</v>
-      </c>
       <c r="G17">
+        <v>20</v>
+      </c>
+      <c r="H17">
         <v>30</v>
       </c>
-      <c r="H17">
+      <c r="I17">
         <v>25</v>
       </c>
-      <c r="I17">
+      <c r="J17">
         <v>45</v>
       </c>
-      <c r="J17">
-        <v>20</v>
-      </c>
       <c r="K17">
+        <v>20</v>
+      </c>
+      <c r="L17">
         <v>30</v>
       </c>
-      <c r="L17">
+      <c r="M17">
         <v>40</v>
       </c>
     </row>
-    <row r="18" spans="1:12" x14ac:dyDescent="0.45">
+    <row r="18" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A18" s="2">
         <v>22</v>
       </c>
@@ -6118,37 +6180,40 @@
         <v>31</v>
       </c>
       <c r="C18" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="D18" t="s">
+        <v>13</v>
+      </c>
+      <c r="E18" t="s">
         <v>17</v>
       </c>
-      <c r="E18" s="2">
-        <v>60</v>
-      </c>
-      <c r="F18">
+      <c r="F18" s="2">
+        <v>60</v>
+      </c>
+      <c r="G18">
         <v>80</v>
       </c>
-      <c r="G18">
-        <v>60</v>
-      </c>
       <c r="H18">
-        <v>20</v>
+        <v>60</v>
       </c>
       <c r="I18">
-        <v>50</v>
+        <v>20</v>
       </c>
       <c r="J18">
-        <v>1</v>
+        <v>50</v>
       </c>
       <c r="K18">
         <v>1</v>
       </c>
       <c r="L18">
+        <v>1</v>
+      </c>
+      <c r="M18">
         <v>40</v>
       </c>
     </row>
-    <row r="19" spans="1:12" x14ac:dyDescent="0.45">
+    <row r="19" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A19" s="2">
         <v>23</v>
       </c>
@@ -6159,34 +6224,37 @@
         <v>13</v>
       </c>
       <c r="D19" t="s">
-        <v>18</v>
-      </c>
-      <c r="E19">
-        <v>50</v>
+        <v>13</v>
+      </c>
+      <c r="E19" t="s">
+        <v>18</v>
       </c>
       <c r="F19">
+        <v>50</v>
+      </c>
+      <c r="G19">
         <v>10</v>
       </c>
-      <c r="G19">
-        <v>60</v>
-      </c>
       <c r="H19">
         <v>60</v>
       </c>
       <c r="I19">
+        <v>60</v>
+      </c>
+      <c r="J19">
         <v>40</v>
       </c>
-      <c r="J19">
-        <v>20</v>
-      </c>
       <c r="K19">
-        <v>60</v>
+        <v>20</v>
       </c>
       <c r="L19">
+        <v>60</v>
+      </c>
+      <c r="M19">
         <v>40</v>
       </c>
     </row>
-    <row r="20" spans="1:12" x14ac:dyDescent="0.45">
+    <row r="20" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A20" s="2">
         <v>24</v>
       </c>
@@ -6197,16 +6265,16 @@
         <v>13</v>
       </c>
       <c r="D20" t="s">
-        <v>18</v>
-      </c>
-      <c r="E20">
-        <v>1</v>
+        <v>13</v>
+      </c>
+      <c r="E20" t="s">
+        <v>18</v>
       </c>
       <c r="F20">
-        <v>50</v>
+        <v>1</v>
       </c>
       <c r="G20">
-        <v>1</v>
+        <v>50</v>
       </c>
       <c r="H20">
         <v>1</v>
@@ -6221,10 +6289,13 @@
         <v>1</v>
       </c>
       <c r="L20">
+        <v>1</v>
+      </c>
+      <c r="M20">
         <v>100</v>
       </c>
     </row>
-    <row r="21" spans="1:12" x14ac:dyDescent="0.45">
+    <row r="21" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A21" s="2">
         <v>25</v>
       </c>
@@ -6232,37 +6303,40 @@
         <v>31</v>
       </c>
       <c r="C21" t="s">
+        <v>14</v>
+      </c>
+      <c r="D21" t="s">
         <v>28</v>
       </c>
-      <c r="D21" t="s">
-        <v>18</v>
-      </c>
-      <c r="E21">
-        <v>40</v>
+      <c r="E21" t="s">
+        <v>18</v>
       </c>
       <c r="F21">
         <v>40</v>
       </c>
       <c r="G21">
+        <v>40</v>
+      </c>
+      <c r="H21">
         <v>70</v>
       </c>
-      <c r="H21">
-        <v>60</v>
-      </c>
       <c r="I21">
         <v>60</v>
       </c>
       <c r="J21">
+        <v>60</v>
+      </c>
+      <c r="K21">
         <v>10</v>
       </c>
-      <c r="K21">
-        <v>60</v>
-      </c>
       <c r="L21">
         <v>60</v>
       </c>
-    </row>
-    <row r="22" spans="1:12" x14ac:dyDescent="0.45">
+      <c r="M21">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="22" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A22" s="2">
         <v>26</v>
       </c>
@@ -6273,34 +6347,37 @@
         <v>13</v>
       </c>
       <c r="D22" t="s">
-        <v>18</v>
-      </c>
-      <c r="E22">
+        <v>13</v>
+      </c>
+      <c r="E22" t="s">
+        <v>18</v>
+      </c>
+      <c r="F22">
         <v>70</v>
       </c>
-      <c r="F22">
+      <c r="G22">
         <v>40</v>
       </c>
-      <c r="G22">
+      <c r="H22">
         <v>65</v>
       </c>
-      <c r="H22">
+      <c r="I22">
         <v>55</v>
       </c>
-      <c r="I22">
-        <v>50</v>
-      </c>
       <c r="J22">
         <v>50</v>
       </c>
       <c r="K22">
-        <v>20</v>
+        <v>50</v>
       </c>
       <c r="L22">
-        <v>50</v>
-      </c>
-    </row>
-    <row r="23" spans="1:12" x14ac:dyDescent="0.45">
+        <v>20</v>
+      </c>
+      <c r="M22">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="23" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A23" s="2">
         <v>27</v>
       </c>
@@ -6308,37 +6385,40 @@
         <v>31</v>
       </c>
       <c r="C23" t="s">
+        <v>13</v>
+      </c>
+      <c r="D23" t="s">
         <v>28</v>
       </c>
-      <c r="D23" t="s">
-        <v>18</v>
-      </c>
-      <c r="E23">
+      <c r="E23" t="s">
+        <v>18</v>
+      </c>
+      <c r="F23">
         <v>85</v>
       </c>
-      <c r="F23">
+      <c r="G23">
         <v>5</v>
       </c>
-      <c r="G23">
+      <c r="H23">
         <v>90</v>
       </c>
-      <c r="H23">
+      <c r="I23">
         <v>2</v>
       </c>
-      <c r="I23">
+      <c r="J23">
         <v>55</v>
       </c>
-      <c r="J23">
+      <c r="K23">
         <v>5</v>
       </c>
-      <c r="K23">
+      <c r="L23">
         <v>2</v>
       </c>
-      <c r="L23">
+      <c r="M23">
         <v>90</v>
       </c>
     </row>
-    <row r="24" spans="1:12" x14ac:dyDescent="0.45">
+    <row r="24" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A24" s="2">
         <v>29</v>
       </c>
@@ -6346,37 +6426,40 @@
         <v>31</v>
       </c>
       <c r="C24" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="D24" t="s">
-        <v>18</v>
-      </c>
-      <c r="E24">
+        <v>13</v>
+      </c>
+      <c r="E24" t="s">
+        <v>18</v>
+      </c>
+      <c r="F24">
         <v>25</v>
       </c>
-      <c r="F24">
-        <v>50</v>
-      </c>
       <c r="G24">
         <v>50</v>
       </c>
       <c r="H24">
+        <v>50</v>
+      </c>
+      <c r="I24">
         <v>40</v>
       </c>
-      <c r="I24">
+      <c r="J24">
         <v>95</v>
       </c>
-      <c r="J24">
+      <c r="K24">
         <v>5</v>
       </c>
-      <c r="K24">
-        <v>1</v>
-      </c>
       <c r="L24">
+        <v>1</v>
+      </c>
+      <c r="M24">
         <v>55</v>
       </c>
     </row>
-    <row r="25" spans="1:12" x14ac:dyDescent="0.45">
+    <row r="25" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A25" s="2">
         <v>30</v>
       </c>
@@ -6387,34 +6470,37 @@
         <v>13</v>
       </c>
       <c r="D25" t="s">
-        <v>18</v>
-      </c>
-      <c r="E25">
+        <v>13</v>
+      </c>
+      <c r="E25" t="s">
+        <v>18</v>
+      </c>
+      <c r="F25">
         <v>23</v>
       </c>
-      <c r="F25">
+      <c r="G25">
         <v>22</v>
       </c>
-      <c r="G25">
+      <c r="H25">
         <v>3</v>
       </c>
-      <c r="H25">
+      <c r="I25">
         <v>77</v>
       </c>
-      <c r="I25">
+      <c r="J25">
         <v>33</v>
       </c>
-      <c r="J25">
+      <c r="K25">
         <v>77</v>
       </c>
-      <c r="K25">
+      <c r="L25">
         <v>3</v>
       </c>
-      <c r="L25">
+      <c r="M25">
         <v>22</v>
       </c>
     </row>
-    <row r="26" spans="1:12" x14ac:dyDescent="0.45">
+    <row r="26" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A26" s="2">
         <v>31</v>
       </c>
@@ -6422,37 +6508,40 @@
         <v>31</v>
       </c>
       <c r="C26" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="D26" t="s">
-        <v>18</v>
-      </c>
-      <c r="E26">
+        <v>13</v>
+      </c>
+      <c r="E26" t="s">
+        <v>18</v>
+      </c>
+      <c r="F26">
         <v>89</v>
       </c>
-      <c r="F26">
-        <v>1</v>
-      </c>
       <c r="G26">
+        <v>1</v>
+      </c>
+      <c r="H26">
         <v>30</v>
       </c>
-      <c r="H26">
+      <c r="I26">
         <v>68</v>
       </c>
-      <c r="I26">
+      <c r="J26">
         <v>30</v>
       </c>
-      <c r="J26">
+      <c r="K26">
         <v>80</v>
       </c>
-      <c r="K26">
+      <c r="L26">
         <v>87</v>
       </c>
-      <c r="L26">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="27" spans="1:12" x14ac:dyDescent="0.45">
+      <c r="M26">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="27" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A27" s="2">
         <v>32</v>
       </c>
@@ -6460,37 +6549,40 @@
         <v>31</v>
       </c>
       <c r="C27" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="D27" t="s">
-        <v>18</v>
-      </c>
-      <c r="E27">
+        <v>13</v>
+      </c>
+      <c r="E27" t="s">
+        <v>18</v>
+      </c>
+      <c r="F27">
         <v>25</v>
       </c>
-      <c r="F27">
+      <c r="G27">
         <v>40</v>
       </c>
-      <c r="G27">
+      <c r="H27">
         <v>70</v>
       </c>
-      <c r="H27">
+      <c r="I27">
         <v>40</v>
       </c>
-      <c r="I27">
+      <c r="J27">
         <v>70</v>
       </c>
-      <c r="J27">
-        <v>1</v>
-      </c>
       <c r="K27">
         <v>1</v>
       </c>
       <c r="L27">
+        <v>1</v>
+      </c>
+      <c r="M27">
         <v>90</v>
       </c>
     </row>
-    <row r="28" spans="1:12" x14ac:dyDescent="0.45">
+    <row r="28" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A28" s="2">
         <v>33</v>
       </c>
@@ -6501,34 +6593,37 @@
         <v>13</v>
       </c>
       <c r="D28" t="s">
-        <v>18</v>
-      </c>
-      <c r="E28">
+        <v>13</v>
+      </c>
+      <c r="E28" t="s">
+        <v>18</v>
+      </c>
+      <c r="F28">
         <v>70</v>
       </c>
-      <c r="F28">
-        <v>1</v>
-      </c>
       <c r="G28">
-        <v>20</v>
+        <v>1</v>
       </c>
       <c r="H28">
-        <v>1</v>
+        <v>20</v>
       </c>
       <c r="I28">
-        <v>20</v>
+        <v>1</v>
       </c>
       <c r="J28">
-        <v>1</v>
+        <v>20</v>
       </c>
       <c r="K28">
         <v>1</v>
       </c>
       <c r="L28">
+        <v>1</v>
+      </c>
+      <c r="M28">
         <v>80</v>
       </c>
     </row>
-    <row r="29" spans="1:12" x14ac:dyDescent="0.45">
+    <row r="29" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A29" s="2">
         <v>34</v>
       </c>
@@ -6539,34 +6634,37 @@
         <v>13</v>
       </c>
       <c r="D29" t="s">
-        <v>18</v>
-      </c>
-      <c r="E29">
+        <v>13</v>
+      </c>
+      <c r="E29" t="s">
+        <v>18</v>
+      </c>
+      <c r="F29">
         <v>40</v>
       </c>
-      <c r="F29">
+      <c r="G29">
         <v>10</v>
       </c>
-      <c r="G29">
+      <c r="H29">
         <v>5</v>
       </c>
-      <c r="H29">
-        <v>50</v>
-      </c>
       <c r="I29">
+        <v>50</v>
+      </c>
+      <c r="J29">
         <v>30</v>
       </c>
-      <c r="J29">
+      <c r="K29">
         <v>0</v>
       </c>
-      <c r="K29">
+      <c r="L29">
         <v>5</v>
       </c>
-      <c r="L29">
-        <v>50</v>
-      </c>
-    </row>
-    <row r="30" spans="1:12" x14ac:dyDescent="0.45">
+      <c r="M29">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="30" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A30" s="2">
         <v>35</v>
       </c>
@@ -6577,34 +6675,37 @@
         <v>13</v>
       </c>
       <c r="D30" t="s">
-        <v>18</v>
-      </c>
-      <c r="E30">
+        <v>13</v>
+      </c>
+      <c r="E30" t="s">
+        <v>18</v>
+      </c>
+      <c r="F30">
         <v>100</v>
       </c>
-      <c r="F30">
+      <c r="G30">
         <v>2</v>
       </c>
-      <c r="G30">
+      <c r="H30">
         <v>100</v>
       </c>
-      <c r="H30">
-        <v>1</v>
-      </c>
       <c r="I30">
+        <v>1</v>
+      </c>
+      <c r="J30">
         <v>80</v>
       </c>
-      <c r="J30">
+      <c r="K30">
         <v>5</v>
       </c>
-      <c r="K30">
-        <v>1</v>
-      </c>
       <c r="L30">
+        <v>1</v>
+      </c>
+      <c r="M30">
         <v>90</v>
       </c>
     </row>
-    <row r="31" spans="1:12" x14ac:dyDescent="0.45">
+    <row r="31" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A31" s="2">
         <v>36</v>
       </c>
@@ -6615,34 +6716,37 @@
         <v>13</v>
       </c>
       <c r="D31" t="s">
-        <v>18</v>
-      </c>
-      <c r="E31">
-        <v>60</v>
+        <v>13</v>
+      </c>
+      <c r="E31" t="s">
+        <v>18</v>
       </c>
       <c r="F31">
+        <v>60</v>
+      </c>
+      <c r="G31">
         <v>30</v>
       </c>
-      <c r="G31">
-        <v>60</v>
-      </c>
       <c r="H31">
-        <v>1</v>
+        <v>60</v>
       </c>
       <c r="I31">
+        <v>1</v>
+      </c>
+      <c r="J31">
         <v>40</v>
       </c>
-      <c r="J31">
-        <v>20</v>
-      </c>
       <c r="K31">
-        <v>60</v>
+        <v>20</v>
       </c>
       <c r="L31">
         <v>60</v>
       </c>
-    </row>
-    <row r="32" spans="1:12" x14ac:dyDescent="0.45">
+      <c r="M31">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="32" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A32" s="2">
         <v>37</v>
       </c>
@@ -6653,34 +6757,37 @@
         <v>13</v>
       </c>
       <c r="D32" t="s">
-        <v>18</v>
-      </c>
-      <c r="E32">
-        <v>60</v>
+        <v>13</v>
+      </c>
+      <c r="E32" t="s">
+        <v>18</v>
       </c>
       <c r="F32">
-        <v>40</v>
+        <v>60</v>
       </c>
       <c r="G32">
         <v>40</v>
       </c>
       <c r="H32">
+        <v>40</v>
+      </c>
+      <c r="I32">
         <v>80</v>
       </c>
-      <c r="I32">
-        <v>50</v>
-      </c>
       <c r="J32">
-        <v>60</v>
+        <v>50</v>
       </c>
       <c r="K32">
-        <v>50</v>
+        <v>60</v>
       </c>
       <c r="L32">
+        <v>50</v>
+      </c>
+      <c r="M32">
         <v>40</v>
       </c>
     </row>
-    <row r="33" spans="1:12" x14ac:dyDescent="0.45">
+    <row r="33" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A33" s="2">
         <v>38</v>
       </c>
@@ -6691,34 +6798,37 @@
         <v>13</v>
       </c>
       <c r="D33" t="s">
-        <v>18</v>
-      </c>
-      <c r="E33">
+        <v>13</v>
+      </c>
+      <c r="E33" t="s">
+        <v>18</v>
+      </c>
+      <c r="F33">
         <v>80</v>
       </c>
-      <c r="F33">
-        <v>1</v>
-      </c>
       <c r="G33">
+        <v>1</v>
+      </c>
+      <c r="H33">
         <v>80</v>
       </c>
-      <c r="H33">
-        <v>1</v>
-      </c>
       <c r="I33">
+        <v>1</v>
+      </c>
+      <c r="J33">
         <v>30</v>
       </c>
-      <c r="J33">
-        <v>1</v>
-      </c>
       <c r="K33">
         <v>1</v>
       </c>
       <c r="L33">
+        <v>1</v>
+      </c>
+      <c r="M33">
         <v>75</v>
       </c>
     </row>
-    <row r="34" spans="1:12" x14ac:dyDescent="0.45">
+    <row r="34" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A34" s="2">
         <v>39</v>
       </c>
@@ -6729,34 +6839,37 @@
         <v>13</v>
       </c>
       <c r="D34" t="s">
-        <v>18</v>
-      </c>
-      <c r="E34">
+        <v>13</v>
+      </c>
+      <c r="E34" t="s">
+        <v>18</v>
+      </c>
+      <c r="F34">
         <v>65</v>
       </c>
-      <c r="F34">
+      <c r="G34">
         <v>55</v>
       </c>
-      <c r="G34">
-        <v>60</v>
-      </c>
       <c r="H34">
+        <v>60</v>
+      </c>
+      <c r="I34">
         <v>65</v>
       </c>
-      <c r="I34">
+      <c r="J34">
         <v>55</v>
       </c>
-      <c r="J34">
+      <c r="K34">
         <v>40</v>
       </c>
-      <c r="K34">
+      <c r="L34">
         <v>30</v>
       </c>
-      <c r="L34">
+      <c r="M34">
         <v>45</v>
       </c>
     </row>
-    <row r="35" spans="1:12" x14ac:dyDescent="0.45">
+    <row r="35" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A35" s="2">
         <v>40</v>
       </c>
@@ -6767,34 +6880,37 @@
         <v>13</v>
       </c>
       <c r="D35" t="s">
-        <v>18</v>
-      </c>
-      <c r="E35">
+        <v>13</v>
+      </c>
+      <c r="E35" t="s">
+        <v>18</v>
+      </c>
+      <c r="F35">
         <v>80</v>
       </c>
-      <c r="F35">
+      <c r="G35">
         <v>75</v>
       </c>
-      <c r="G35">
-        <v>60</v>
-      </c>
       <c r="H35">
+        <v>60</v>
+      </c>
+      <c r="I35">
         <v>10</v>
       </c>
-      <c r="I35">
-        <v>60</v>
-      </c>
       <c r="J35">
-        <v>50</v>
+        <v>60</v>
       </c>
       <c r="K35">
+        <v>50</v>
+      </c>
+      <c r="L35">
         <v>10</v>
       </c>
-      <c r="L35">
+      <c r="M35">
         <v>80</v>
       </c>
     </row>
-    <row r="36" spans="1:12" x14ac:dyDescent="0.45">
+    <row r="36" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A36" s="2">
         <v>41</v>
       </c>
@@ -6802,37 +6918,40 @@
         <v>31</v>
       </c>
       <c r="C36" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="D36" t="s">
-        <v>18</v>
-      </c>
-      <c r="E36">
+        <v>13</v>
+      </c>
+      <c r="E36" t="s">
+        <v>18</v>
+      </c>
+      <c r="F36">
         <v>80</v>
       </c>
-      <c r="F36">
+      <c r="G36">
         <v>100</v>
       </c>
-      <c r="G36">
+      <c r="H36">
         <v>90</v>
       </c>
-      <c r="H36">
-        <v>1</v>
-      </c>
       <c r="I36">
+        <v>1</v>
+      </c>
+      <c r="J36">
         <v>80</v>
       </c>
-      <c r="J36">
-        <v>1</v>
-      </c>
       <c r="K36">
         <v>1</v>
       </c>
       <c r="L36">
+        <v>1</v>
+      </c>
+      <c r="M36">
         <v>100</v>
       </c>
     </row>
-    <row r="37" spans="1:12" x14ac:dyDescent="0.45">
+    <row r="37" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A37" s="2">
         <v>42</v>
       </c>
@@ -6840,37 +6959,40 @@
         <v>31</v>
       </c>
       <c r="C37" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="D37" t="s">
-        <v>18</v>
-      </c>
-      <c r="E37">
+        <v>13</v>
+      </c>
+      <c r="E37" t="s">
+        <v>18</v>
+      </c>
+      <c r="F37">
         <v>90</v>
       </c>
-      <c r="F37">
+      <c r="G37">
         <v>30</v>
       </c>
-      <c r="G37">
+      <c r="H37">
         <v>90</v>
       </c>
-      <c r="H37">
+      <c r="I37">
         <v>10</v>
       </c>
-      <c r="I37">
+      <c r="J37">
         <v>70</v>
-      </c>
-      <c r="J37">
-        <v>2</v>
       </c>
       <c r="K37">
         <v>2</v>
       </c>
       <c r="L37">
+        <v>2</v>
+      </c>
+      <c r="M37">
         <v>95</v>
       </c>
     </row>
-    <row r="38" spans="1:12" x14ac:dyDescent="0.45">
+    <row r="38" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A38" s="2">
         <v>43</v>
       </c>
@@ -6881,34 +7003,37 @@
         <v>13</v>
       </c>
       <c r="D38" t="s">
-        <v>18</v>
-      </c>
-      <c r="E38">
-        <v>20</v>
+        <v>13</v>
+      </c>
+      <c r="E38" t="s">
+        <v>18</v>
       </c>
       <c r="F38">
-        <v>1</v>
+        <v>20</v>
       </c>
       <c r="G38">
+        <v>1</v>
+      </c>
+      <c r="H38">
         <v>90</v>
       </c>
-      <c r="H38">
-        <v>1</v>
-      </c>
       <c r="I38">
+        <v>1</v>
+      </c>
+      <c r="J38">
         <v>10</v>
       </c>
-      <c r="J38">
-        <v>1</v>
-      </c>
       <c r="K38">
+        <v>1</v>
+      </c>
+      <c r="L38">
         <v>5</v>
       </c>
-      <c r="L38">
+      <c r="M38">
         <v>80</v>
       </c>
     </row>
-    <row r="39" spans="1:12" x14ac:dyDescent="0.45">
+    <row r="39" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A39" s="2">
         <v>44</v>
       </c>
@@ -6919,34 +7044,37 @@
         <v>13</v>
       </c>
       <c r="D39" t="s">
-        <v>18</v>
-      </c>
-      <c r="E39">
+        <v>13</v>
+      </c>
+      <c r="E39" t="s">
+        <v>18</v>
+      </c>
+      <c r="F39">
         <v>7</v>
       </c>
-      <c r="F39">
+      <c r="G39">
         <v>66</v>
       </c>
-      <c r="G39">
+      <c r="H39">
         <v>80</v>
       </c>
-      <c r="H39">
-        <v>1</v>
-      </c>
       <c r="I39">
+        <v>1</v>
+      </c>
+      <c r="J39">
         <v>7</v>
       </c>
-      <c r="J39">
-        <v>1</v>
-      </c>
       <c r="K39">
         <v>1</v>
       </c>
       <c r="L39">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="40" spans="1:12" x14ac:dyDescent="0.45">
+        <v>1</v>
+      </c>
+      <c r="M39">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="40" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A40" s="2">
         <v>45</v>
       </c>
@@ -6957,34 +7085,37 @@
         <v>13</v>
       </c>
       <c r="D40" t="s">
+        <v>13</v>
+      </c>
+      <c r="E40" t="s">
         <v>17</v>
       </c>
-      <c r="E40">
+      <c r="F40">
         <v>90</v>
       </c>
-      <c r="F40">
-        <v>1</v>
-      </c>
       <c r="G40">
+        <v>1</v>
+      </c>
+      <c r="H40">
         <v>90</v>
       </c>
-      <c r="H40">
+      <c r="I40">
         <v>10</v>
       </c>
-      <c r="I40">
+      <c r="J40">
         <v>85</v>
       </c>
-      <c r="J40">
-        <v>1</v>
-      </c>
       <c r="K40">
+        <v>1</v>
+      </c>
+      <c r="L40">
         <v>2</v>
       </c>
-      <c r="L40">
+      <c r="M40">
         <v>90</v>
       </c>
     </row>
-    <row r="41" spans="1:12" x14ac:dyDescent="0.45">
+    <row r="41" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A41" s="2">
         <v>46</v>
       </c>
@@ -6995,34 +7126,37 @@
         <v>13</v>
       </c>
       <c r="D41" t="s">
-        <v>18</v>
-      </c>
-      <c r="E41">
+        <v>13</v>
+      </c>
+      <c r="E41" t="s">
+        <v>18</v>
+      </c>
+      <c r="F41">
         <v>70</v>
       </c>
-      <c r="F41">
-        <v>20</v>
-      </c>
       <c r="G41">
-        <v>60</v>
+        <v>20</v>
       </c>
       <c r="H41">
-        <v>50</v>
+        <v>60</v>
       </c>
       <c r="I41">
         <v>50</v>
       </c>
       <c r="J41">
+        <v>50</v>
+      </c>
+      <c r="K41">
         <v>10</v>
-      </c>
-      <c r="K41">
-        <v>30</v>
       </c>
       <c r="L41">
         <v>30</v>
       </c>
-    </row>
-    <row r="42" spans="1:12" x14ac:dyDescent="0.45">
+      <c r="M41">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="42" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A42" s="2">
         <v>47</v>
       </c>
@@ -7033,34 +7167,37 @@
         <v>13</v>
       </c>
       <c r="D42" t="s">
-        <v>18</v>
-      </c>
-      <c r="E42">
-        <v>50</v>
+        <v>13</v>
+      </c>
+      <c r="E42" t="s">
+        <v>18</v>
       </c>
       <c r="F42">
+        <v>50</v>
+      </c>
+      <c r="G42">
         <v>80</v>
       </c>
-      <c r="G42">
+      <c r="H42">
         <v>90</v>
       </c>
-      <c r="H42">
+      <c r="I42">
         <v>70</v>
       </c>
-      <c r="I42">
+      <c r="J42">
         <v>65</v>
       </c>
-      <c r="J42">
-        <v>1</v>
-      </c>
       <c r="K42">
         <v>1</v>
       </c>
       <c r="L42">
+        <v>1</v>
+      </c>
+      <c r="M42">
         <v>95</v>
       </c>
     </row>
-    <row r="43" spans="1:12" x14ac:dyDescent="0.45">
+    <row r="43" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A43" s="2">
         <v>48</v>
       </c>
@@ -7071,31 +7208,34 @@
         <v>13</v>
       </c>
       <c r="D43" t="s">
-        <v>18</v>
-      </c>
-      <c r="E43">
-        <v>60</v>
+        <v>13</v>
+      </c>
+      <c r="E43" t="s">
+        <v>18</v>
       </c>
       <c r="F43">
-        <v>1</v>
+        <v>60</v>
       </c>
       <c r="G43">
-        <v>50</v>
+        <v>1</v>
       </c>
       <c r="H43">
         <v>50</v>
       </c>
-      <c r="J43">
+      <c r="I43">
+        <v>50</v>
+      </c>
+      <c r="K43">
         <v>70</v>
       </c>
-      <c r="K43">
-        <v>1</v>
-      </c>
       <c r="L43">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="44" spans="1:12" x14ac:dyDescent="0.45">
+        <v>1</v>
+      </c>
+      <c r="M43">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="44" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A44" s="2">
         <v>49</v>
       </c>
@@ -7106,20 +7246,20 @@
         <v>13</v>
       </c>
       <c r="D44" t="s">
-        <v>18</v>
-      </c>
-      <c r="E44">
+        <v>13</v>
+      </c>
+      <c r="E44" t="s">
+        <v>18</v>
+      </c>
+      <c r="F44">
         <v>95</v>
       </c>
-      <c r="F44">
+      <c r="G44">
         <v>45</v>
       </c>
-      <c r="G44">
+      <c r="H44">
         <v>90</v>
       </c>
-      <c r="H44">
-        <v>1</v>
-      </c>
       <c r="I44">
         <v>1</v>
       </c>
@@ -7130,10 +7270,13 @@
         <v>1</v>
       </c>
       <c r="L44">
+        <v>1</v>
+      </c>
+      <c r="M44">
         <v>85</v>
       </c>
     </row>
-    <row r="45" spans="1:12" x14ac:dyDescent="0.45">
+    <row r="45" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A45" s="2">
         <v>50</v>
       </c>
@@ -7144,34 +7287,37 @@
         <v>13</v>
       </c>
       <c r="D45" t="s">
-        <v>18</v>
-      </c>
-      <c r="E45">
-        <v>50</v>
+        <v>13</v>
+      </c>
+      <c r="E45" t="s">
+        <v>18</v>
       </c>
       <c r="F45">
+        <v>50</v>
+      </c>
+      <c r="G45">
         <v>30</v>
       </c>
-      <c r="G45">
-        <v>60</v>
-      </c>
       <c r="H45">
+        <v>60</v>
+      </c>
+      <c r="I45">
         <v>30</v>
       </c>
-      <c r="I45">
-        <v>60</v>
-      </c>
       <c r="J45">
-        <v>20</v>
+        <v>60</v>
       </c>
       <c r="K45">
         <v>20</v>
       </c>
       <c r="L45">
+        <v>20</v>
+      </c>
+      <c r="M45">
         <v>30</v>
       </c>
     </row>
-    <row r="46" spans="1:12" x14ac:dyDescent="0.45">
+    <row r="46" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A46" s="2">
         <v>51</v>
       </c>
@@ -7182,16 +7328,16 @@
         <v>13</v>
       </c>
       <c r="D46" t="s">
-        <v>18</v>
-      </c>
-      <c r="E46">
+        <v>13</v>
+      </c>
+      <c r="E46" t="s">
+        <v>18</v>
+      </c>
+      <c r="F46">
         <v>40</v>
       </c>
-      <c r="F46">
+      <c r="G46">
         <v>10</v>
-      </c>
-      <c r="G46">
-        <v>70</v>
       </c>
       <c r="H46">
         <v>70</v>
@@ -7200,16 +7346,19 @@
         <v>70</v>
       </c>
       <c r="J46">
-        <v>50</v>
+        <v>70</v>
       </c>
       <c r="K46">
+        <v>50</v>
+      </c>
+      <c r="L46">
         <v>10</v>
       </c>
-      <c r="L46">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="47" spans="1:12" x14ac:dyDescent="0.45">
+      <c r="M46">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="47" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A47" s="2">
         <v>52</v>
       </c>
@@ -7220,17 +7369,17 @@
         <v>13</v>
       </c>
       <c r="D47" t="s">
-        <v>18</v>
-      </c>
-      <c r="E47">
-        <v>60</v>
+        <v>13</v>
+      </c>
+      <c r="E47" t="s">
+        <v>18</v>
       </c>
       <c r="F47">
+        <v>60</v>
+      </c>
+      <c r="G47">
         <v>10</v>
       </c>
-      <c r="G47">
-        <v>20</v>
-      </c>
       <c r="H47">
         <v>20</v>
       </c>
@@ -7238,16 +7387,19 @@
         <v>20</v>
       </c>
       <c r="J47">
+        <v>20</v>
+      </c>
+      <c r="K47">
         <v>10</v>
       </c>
-      <c r="K47">
-        <v>20</v>
-      </c>
       <c r="L47">
+        <v>20</v>
+      </c>
+      <c r="M47">
         <v>30</v>
       </c>
     </row>
-    <row r="48" spans="1:12" x14ac:dyDescent="0.45">
+    <row r="48" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A48" s="2">
         <v>53</v>
       </c>
@@ -7258,34 +7410,37 @@
         <v>13</v>
       </c>
       <c r="D48" t="s">
-        <v>18</v>
-      </c>
-      <c r="E48">
+        <v>13</v>
+      </c>
+      <c r="E48" t="s">
+        <v>18</v>
+      </c>
+      <c r="F48">
         <v>80</v>
       </c>
-      <c r="F48">
+      <c r="G48">
         <v>25</v>
       </c>
-      <c r="G48">
+      <c r="H48">
         <v>80</v>
       </c>
-      <c r="H48">
+      <c r="I48">
         <v>10</v>
       </c>
-      <c r="I48">
+      <c r="J48">
         <v>75</v>
       </c>
-      <c r="J48">
-        <v>1</v>
-      </c>
       <c r="K48">
+        <v>1</v>
+      </c>
+      <c r="L48">
         <v>35</v>
       </c>
-      <c r="L48">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="49" spans="1:12" x14ac:dyDescent="0.45">
+      <c r="M48">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="49" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A49" s="2">
         <v>54</v>
       </c>
@@ -7293,37 +7448,40 @@
         <v>31</v>
       </c>
       <c r="C49" t="s">
+        <v>14</v>
+      </c>
+      <c r="D49" t="s">
         <v>28</v>
       </c>
-      <c r="D49" t="s">
-        <v>18</v>
-      </c>
-      <c r="E49">
-        <v>50</v>
+      <c r="E49" t="s">
+        <v>18</v>
       </c>
       <c r="F49">
-        <v>20</v>
+        <v>50</v>
       </c>
       <c r="G49">
+        <v>20</v>
+      </c>
+      <c r="H49">
         <v>80</v>
       </c>
-      <c r="H49">
-        <v>20</v>
-      </c>
       <c r="I49">
-        <v>50</v>
+        <v>20</v>
       </c>
       <c r="J49">
-        <v>1</v>
+        <v>50</v>
       </c>
       <c r="K49">
-        <v>50</v>
+        <v>1</v>
       </c>
       <c r="L49">
         <v>50</v>
       </c>
-    </row>
-    <row r="50" spans="1:12" x14ac:dyDescent="0.45">
+      <c r="M49">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="50" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A50" s="2">
         <v>55</v>
       </c>
@@ -7331,37 +7489,40 @@
         <v>31</v>
       </c>
       <c r="C50" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="D50" t="s">
-        <v>18</v>
-      </c>
-      <c r="E50">
+        <v>13</v>
+      </c>
+      <c r="E50" t="s">
+        <v>18</v>
+      </c>
+      <c r="F50">
         <v>85</v>
       </c>
-      <c r="F50">
-        <v>50</v>
-      </c>
       <c r="G50">
+        <v>50</v>
+      </c>
+      <c r="H50">
         <v>80</v>
       </c>
-      <c r="H50">
+      <c r="I50">
         <v>40</v>
       </c>
-      <c r="I50">
+      <c r="J50">
         <v>70</v>
       </c>
-      <c r="J50">
-        <v>1</v>
-      </c>
       <c r="K50">
+        <v>1</v>
+      </c>
+      <c r="L50">
         <v>70</v>
       </c>
-      <c r="L50">
+      <c r="M50">
         <v>30</v>
       </c>
     </row>
-    <row r="51" spans="1:12" x14ac:dyDescent="0.45">
+    <row r="51" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A51" s="2">
         <v>56</v>
       </c>
@@ -7369,37 +7530,40 @@
         <v>31</v>
       </c>
       <c r="C51" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="D51" t="s">
-        <v>18</v>
-      </c>
-      <c r="E51">
+        <v>13</v>
+      </c>
+      <c r="E51" t="s">
+        <v>18</v>
+      </c>
+      <c r="F51">
         <v>80</v>
       </c>
-      <c r="F51">
+      <c r="G51">
         <v>30</v>
       </c>
-      <c r="G51">
+      <c r="H51">
         <v>80</v>
       </c>
-      <c r="H51">
-        <v>1</v>
-      </c>
       <c r="I51">
+        <v>1</v>
+      </c>
+      <c r="J51">
         <v>70</v>
       </c>
-      <c r="J51">
-        <v>1</v>
-      </c>
       <c r="K51">
+        <v>1</v>
+      </c>
+      <c r="L51">
         <v>30</v>
       </c>
-      <c r="L51">
+      <c r="M51">
         <v>70</v>
       </c>
     </row>
-    <row r="52" spans="1:12" x14ac:dyDescent="0.45">
+    <row r="52" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A52" s="2">
         <v>57</v>
       </c>
@@ -7407,37 +7571,40 @@
         <v>31</v>
       </c>
       <c r="C52" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="D52" t="s">
-        <v>18</v>
-      </c>
-      <c r="E52">
+        <v>13</v>
+      </c>
+      <c r="E52" t="s">
+        <v>18</v>
+      </c>
+      <c r="F52">
         <v>75</v>
       </c>
-      <c r="F52">
+      <c r="G52">
         <v>79</v>
       </c>
-      <c r="G52">
+      <c r="H52">
         <v>68</v>
       </c>
-      <c r="H52">
+      <c r="I52">
         <v>31</v>
       </c>
-      <c r="I52">
+      <c r="J52">
         <v>80</v>
       </c>
-      <c r="J52">
+      <c r="K52">
         <v>15</v>
       </c>
-      <c r="K52">
+      <c r="L52">
         <v>10</v>
       </c>
-      <c r="L52">
+      <c r="M52">
         <v>70</v>
       </c>
     </row>
-    <row r="53" spans="1:12" x14ac:dyDescent="0.45">
+    <row r="53" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A53" s="2">
         <v>58</v>
       </c>
@@ -7445,37 +7612,40 @@
         <v>31</v>
       </c>
       <c r="C53" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="D53" t="s">
-        <v>18</v>
-      </c>
-      <c r="E53">
+        <v>13</v>
+      </c>
+      <c r="E53" t="s">
+        <v>18</v>
+      </c>
+      <c r="F53">
         <v>80</v>
       </c>
-      <c r="F53">
-        <v>1</v>
-      </c>
       <c r="G53">
+        <v>1</v>
+      </c>
+      <c r="H53">
         <v>80</v>
       </c>
-      <c r="H53">
-        <v>1</v>
-      </c>
       <c r="I53">
-        <v>50</v>
+        <v>1</v>
       </c>
       <c r="J53">
-        <v>1</v>
+        <v>50</v>
       </c>
       <c r="K53">
+        <v>1</v>
+      </c>
+      <c r="L53">
         <v>30</v>
       </c>
-      <c r="L53">
+      <c r="M53">
         <v>80</v>
       </c>
     </row>
-    <row r="54" spans="1:12" x14ac:dyDescent="0.45">
+    <row r="54" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A54" s="2">
         <v>59</v>
       </c>
@@ -7483,37 +7653,40 @@
         <v>31</v>
       </c>
       <c r="C54" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="D54" t="s">
-        <v>18</v>
-      </c>
-      <c r="E54">
+        <v>13</v>
+      </c>
+      <c r="E54" t="s">
+        <v>18</v>
+      </c>
+      <c r="F54">
         <v>80</v>
       </c>
-      <c r="F54">
+      <c r="G54">
         <v>40</v>
       </c>
-      <c r="G54">
+      <c r="H54">
         <v>30</v>
       </c>
-      <c r="H54">
-        <v>60</v>
-      </c>
       <c r="I54">
+        <v>60</v>
+      </c>
+      <c r="J54">
         <v>30</v>
       </c>
-      <c r="J54">
-        <v>50</v>
-      </c>
       <c r="K54">
-        <v>60</v>
+        <v>50</v>
       </c>
       <c r="L54">
+        <v>60</v>
+      </c>
+      <c r="M54">
         <v>30</v>
       </c>
     </row>
-    <row r="55" spans="1:12" x14ac:dyDescent="0.45">
+    <row r="55" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A55" s="2">
         <v>60</v>
       </c>
@@ -7521,37 +7694,40 @@
         <v>31</v>
       </c>
       <c r="C55" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="D55" t="s">
-        <v>18</v>
-      </c>
-      <c r="E55">
+        <v>13</v>
+      </c>
+      <c r="E55" t="s">
+        <v>18</v>
+      </c>
+      <c r="F55">
         <v>30</v>
       </c>
-      <c r="F55">
+      <c r="G55">
         <v>10</v>
       </c>
-      <c r="G55">
+      <c r="H55">
         <v>70</v>
       </c>
-      <c r="H55">
-        <v>1</v>
-      </c>
       <c r="I55">
-        <v>20</v>
+        <v>1</v>
       </c>
       <c r="J55">
-        <v>1</v>
+        <v>20</v>
       </c>
       <c r="K55">
-        <v>20</v>
+        <v>1</v>
       </c>
       <c r="L55">
+        <v>20</v>
+      </c>
+      <c r="M55">
         <v>70</v>
       </c>
     </row>
-    <row r="56" spans="1:12" x14ac:dyDescent="0.45">
+    <row r="56" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A56" s="2">
         <v>61</v>
       </c>
@@ -7559,37 +7735,40 @@
         <v>31</v>
       </c>
       <c r="C56" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="D56" t="s">
-        <v>18</v>
-      </c>
-      <c r="E56">
+        <v>13</v>
+      </c>
+      <c r="E56" t="s">
+        <v>18</v>
+      </c>
+      <c r="F56">
         <v>75</v>
       </c>
-      <c r="F56">
-        <v>50</v>
-      </c>
       <c r="G56">
+        <v>50</v>
+      </c>
+      <c r="H56">
         <v>40</v>
       </c>
-      <c r="H56">
+      <c r="I56">
         <v>90</v>
       </c>
-      <c r="I56">
-        <v>20</v>
-      </c>
       <c r="J56">
+        <v>20</v>
+      </c>
+      <c r="K56">
         <v>65</v>
       </c>
-      <c r="K56">
+      <c r="L56">
         <v>70</v>
       </c>
-      <c r="L56">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="57" spans="1:12" x14ac:dyDescent="0.45">
+      <c r="M56">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="57" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A57" s="2">
         <v>62</v>
       </c>
@@ -7597,37 +7776,40 @@
         <v>31</v>
       </c>
       <c r="C57" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="D57" t="s">
-        <v>18</v>
-      </c>
-      <c r="E57">
+        <v>13</v>
+      </c>
+      <c r="E57" t="s">
+        <v>18</v>
+      </c>
+      <c r="F57">
         <v>40</v>
       </c>
-      <c r="F57">
-        <v>60</v>
-      </c>
       <c r="G57">
+        <v>60</v>
+      </c>
+      <c r="H57">
         <v>70</v>
-      </c>
-      <c r="H57">
-        <v>40</v>
       </c>
       <c r="I57">
         <v>40</v>
       </c>
       <c r="J57">
-        <v>20</v>
+        <v>40</v>
       </c>
       <c r="K57">
+        <v>20</v>
+      </c>
+      <c r="L57">
         <v>30</v>
       </c>
-      <c r="L57">
+      <c r="M57">
         <v>70</v>
       </c>
     </row>
-    <row r="58" spans="1:12" x14ac:dyDescent="0.45">
+    <row r="58" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A58" s="2">
         <v>63</v>
       </c>
@@ -7635,37 +7817,40 @@
         <v>31</v>
       </c>
       <c r="C58" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="D58" t="s">
+        <v>13</v>
+      </c>
+      <c r="E58" t="s">
         <v>17</v>
       </c>
-      <c r="E58">
-        <v>50</v>
-      </c>
       <c r="F58">
-        <v>20</v>
+        <v>50</v>
       </c>
       <c r="G58">
+        <v>20</v>
+      </c>
+      <c r="H58">
         <v>30</v>
       </c>
-      <c r="H58">
-        <v>60</v>
-      </c>
       <c r="I58">
+        <v>60</v>
+      </c>
+      <c r="J58">
         <v>40</v>
       </c>
-      <c r="J58">
-        <v>50</v>
-      </c>
       <c r="K58">
+        <v>50</v>
+      </c>
+      <c r="L58">
         <v>10</v>
       </c>
-      <c r="L58">
+      <c r="M58">
         <v>40</v>
       </c>
     </row>
-    <row r="59" spans="1:12" x14ac:dyDescent="0.45">
+    <row r="59" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A59" s="2">
         <v>64</v>
       </c>
@@ -7673,37 +7858,40 @@
         <v>31</v>
       </c>
       <c r="C59" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="D59" t="s">
-        <v>18</v>
-      </c>
-      <c r="E59">
-        <v>30</v>
+        <v>13</v>
+      </c>
+      <c r="E59" t="s">
+        <v>18</v>
       </c>
       <c r="F59">
         <v>30</v>
       </c>
       <c r="G59">
+        <v>30</v>
+      </c>
+      <c r="H59">
         <v>40</v>
       </c>
-      <c r="H59">
+      <c r="I59">
         <v>10</v>
       </c>
-      <c r="I59">
+      <c r="J59">
         <v>30</v>
       </c>
-      <c r="J59">
+      <c r="K59">
         <v>10</v>
       </c>
-      <c r="K59">
-        <v>60</v>
-      </c>
       <c r="L59">
-        <v>50</v>
-      </c>
-    </row>
-    <row r="60" spans="1:12" x14ac:dyDescent="0.45">
+        <v>60</v>
+      </c>
+      <c r="M59">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="60" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A60" s="2">
         <v>65</v>
       </c>
@@ -7711,37 +7899,40 @@
         <v>31</v>
       </c>
       <c r="C60" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="D60" t="s">
-        <v>18</v>
-      </c>
-      <c r="E60">
+        <v>13</v>
+      </c>
+      <c r="E60" t="s">
+        <v>18</v>
+      </c>
+      <c r="F60">
         <v>90</v>
       </c>
-      <c r="F60">
-        <v>60</v>
-      </c>
       <c r="G60">
+        <v>60</v>
+      </c>
+      <c r="H60">
         <v>80</v>
       </c>
-      <c r="H60">
-        <v>1</v>
-      </c>
       <c r="I60">
-        <v>50</v>
+        <v>1</v>
       </c>
       <c r="J60">
-        <v>1</v>
+        <v>50</v>
       </c>
       <c r="K60">
         <v>1</v>
       </c>
       <c r="L60">
+        <v>1</v>
+      </c>
+      <c r="M60">
         <v>90</v>
       </c>
     </row>
-    <row r="61" spans="1:12" x14ac:dyDescent="0.45">
+    <row r="61" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A61" s="2">
         <v>66</v>
       </c>
@@ -7749,34 +7940,37 @@
         <v>31</v>
       </c>
       <c r="C61" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="D61" t="s">
-        <v>18</v>
-      </c>
-      <c r="E61">
+        <v>13</v>
+      </c>
+      <c r="E61" t="s">
+        <v>18</v>
+      </c>
+      <c r="F61">
         <v>80</v>
       </c>
-      <c r="F61">
-        <v>20</v>
-      </c>
       <c r="G61">
+        <v>20</v>
+      </c>
+      <c r="H61">
         <v>80</v>
-      </c>
-      <c r="H61">
-        <v>30</v>
       </c>
       <c r="I61">
         <v>30</v>
       </c>
       <c r="J61">
-        <v>20</v>
+        <v>30</v>
       </c>
       <c r="K61">
+        <v>20</v>
+      </c>
+      <c r="L61">
         <v>30</v>
       </c>
     </row>
-    <row r="62" spans="1:12" x14ac:dyDescent="0.45">
+    <row r="62" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A62" s="2">
         <v>67</v>
       </c>
@@ -7784,37 +7978,40 @@
         <v>31</v>
       </c>
       <c r="C62" t="s">
+        <v>14</v>
+      </c>
+      <c r="D62" t="s">
         <v>28</v>
       </c>
-      <c r="D62" t="s">
-        <v>18</v>
-      </c>
-      <c r="E62">
-        <v>60</v>
+      <c r="E62" t="s">
+        <v>18</v>
       </c>
       <c r="F62">
-        <v>20</v>
+        <v>60</v>
       </c>
       <c r="G62">
+        <v>20</v>
+      </c>
+      <c r="H62">
         <v>80</v>
       </c>
-      <c r="H62">
-        <v>1</v>
-      </c>
       <c r="I62">
+        <v>1</v>
+      </c>
+      <c r="J62">
         <v>30</v>
       </c>
-      <c r="J62">
-        <v>1</v>
-      </c>
       <c r="K62">
         <v>1</v>
       </c>
       <c r="L62">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="63" spans="1:12" x14ac:dyDescent="0.45">
+        <v>1</v>
+      </c>
+      <c r="M62">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="63" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A63" s="2">
         <v>68</v>
       </c>
@@ -7822,37 +8019,40 @@
         <v>31</v>
       </c>
       <c r="C63" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="D63" t="s">
-        <v>18</v>
-      </c>
-      <c r="E63">
+        <v>13</v>
+      </c>
+      <c r="E63" t="s">
+        <v>18</v>
+      </c>
+      <c r="F63">
         <v>90</v>
       </c>
-      <c r="F63">
-        <v>50</v>
-      </c>
       <c r="G63">
+        <v>50</v>
+      </c>
+      <c r="H63">
         <v>70</v>
       </c>
-      <c r="H63">
+      <c r="I63">
         <v>40</v>
       </c>
-      <c r="I63">
-        <v>50</v>
-      </c>
       <c r="J63">
-        <v>4</v>
+        <v>50</v>
       </c>
       <c r="K63">
         <v>4</v>
       </c>
       <c r="L63">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="64" spans="1:12" x14ac:dyDescent="0.45">
+        <v>4</v>
+      </c>
+      <c r="M63">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="64" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A64" s="2">
         <v>69</v>
       </c>
@@ -7860,37 +8060,40 @@
         <v>31</v>
       </c>
       <c r="C64" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="D64" t="s">
-        <v>18</v>
-      </c>
-      <c r="E64">
+        <v>13</v>
+      </c>
+      <c r="E64" t="s">
+        <v>18</v>
+      </c>
+      <c r="F64">
         <v>80</v>
       </c>
-      <c r="F64">
-        <v>20</v>
-      </c>
       <c r="G64">
+        <v>20</v>
+      </c>
+      <c r="H64">
         <v>80</v>
       </c>
-      <c r="H64">
+      <c r="I64">
         <v>10</v>
       </c>
-      <c r="I64">
-        <v>20</v>
-      </c>
       <c r="J64">
         <v>20</v>
       </c>
       <c r="K64">
+        <v>20</v>
+      </c>
+      <c r="L64">
         <v>10</v>
       </c>
-      <c r="L64">
+      <c r="M64">
         <v>80</v>
       </c>
     </row>
-    <row r="65" spans="1:12" x14ac:dyDescent="0.45">
+    <row r="65" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A65" s="2">
         <v>70</v>
       </c>
@@ -7898,37 +8101,40 @@
         <v>31</v>
       </c>
       <c r="C65" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="D65" t="s">
-        <v>18</v>
-      </c>
-      <c r="E65">
+        <v>13</v>
+      </c>
+      <c r="E65" t="s">
+        <v>18</v>
+      </c>
+      <c r="F65">
         <v>90</v>
       </c>
-      <c r="F65">
+      <c r="G65">
         <v>30</v>
       </c>
-      <c r="G65">
+      <c r="H65">
         <v>88</v>
       </c>
-      <c r="H65">
+      <c r="I65">
         <v>10</v>
       </c>
-      <c r="I65">
-        <v>60</v>
-      </c>
       <c r="J65">
+        <v>60</v>
+      </c>
+      <c r="K65">
         <v>5</v>
       </c>
-      <c r="K65">
+      <c r="L65">
         <v>40</v>
       </c>
-      <c r="L65">
+      <c r="M65">
         <v>77</v>
       </c>
     </row>
-    <row r="66" spans="1:12" x14ac:dyDescent="0.45">
+    <row r="66" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A66" s="2">
         <v>71</v>
       </c>
@@ -7936,37 +8142,40 @@
         <v>31</v>
       </c>
       <c r="C66" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="D66" t="s">
-        <v>18</v>
-      </c>
-      <c r="E66">
+        <v>13</v>
+      </c>
+      <c r="E66" t="s">
+        <v>18</v>
+      </c>
+      <c r="F66">
         <v>82</v>
       </c>
-      <c r="F66">
+      <c r="G66">
         <v>8</v>
       </c>
-      <c r="G66">
+      <c r="H66">
         <v>65</v>
       </c>
-      <c r="H66">
-        <v>50</v>
-      </c>
       <c r="I66">
         <v>50</v>
       </c>
       <c r="J66">
+        <v>50</v>
+      </c>
+      <c r="K66">
         <v>25</v>
       </c>
-      <c r="K66">
+      <c r="L66">
         <v>24</v>
       </c>
-      <c r="L66">
+      <c r="M66">
         <v>64</v>
       </c>
     </row>
-    <row r="67" spans="1:12" x14ac:dyDescent="0.45">
+    <row r="67" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A67" s="2">
         <v>72</v>
       </c>
@@ -7974,13 +8183,13 @@
         <v>31</v>
       </c>
       <c r="C67" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="D67" t="s">
-        <v>18</v>
-      </c>
-      <c r="E67">
-        <v>70</v>
+        <v>13</v>
+      </c>
+      <c r="E67" t="s">
+        <v>18</v>
       </c>
       <c r="F67">
         <v>70</v>
@@ -7989,23 +8198,26 @@
         <v>70</v>
       </c>
       <c r="H67">
+        <v>70</v>
+      </c>
+      <c r="I67">
         <v>40</v>
       </c>
-      <c r="I67">
+      <c r="J67">
         <v>70</v>
       </c>
-      <c r="J67">
-        <v>50</v>
-      </c>
       <c r="K67">
+        <v>50</v>
+      </c>
+      <c r="L67">
         <v>70</v>
       </c>
-      <c r="L67">
+      <c r="M67">
         <v>75</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:L67" xr:uid="{26FAC1FF-5E09-4135-A43D-31190E34F3D4}"/>
+  <autoFilter ref="A1:M67" xr:uid="{26FAC1FF-5E09-4135-A43D-31190E34F3D4}"/>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -8013,20 +8225,21 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9D83972C-8AA1-494E-8B24-51FD46390AC9}">
-  <dimension ref="A1:L67"/>
-  <sheetFormatPr defaultRowHeight="14" x14ac:dyDescent="0.45"/>
+  <dimension ref="A1:M67"/>
+  <sheetFormatPr defaultRowHeight="13.9" x14ac:dyDescent="0.4"/>
   <cols>
-    <col min="1" max="1" width="13.52734375" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="13.1171875" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="13.87890625" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="15.52734375" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="15.64453125" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="11.234375" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="6.76171875" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="7.64453125" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="13.53125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="13.1328125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="10.6640625" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="13.86328125" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="15.53125" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="15.6640625" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="11.19921875" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="6.73046875" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="7.6640625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:12" x14ac:dyDescent="0.45">
+    <row r="1" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -8034,37 +8247,40 @@
         <v>30</v>
       </c>
       <c r="C1" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="D1" s="1" t="s">
+      <c r="E1" s="1" t="s">
         <v>29</v>
       </c>
-      <c r="E1" s="1" t="s">
-        <v>20</v>
-      </c>
       <c r="F1" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="G1" s="1" t="s">
         <v>21</v>
       </c>
-      <c r="G1" s="1" t="s">
+      <c r="H1" s="1" t="s">
         <v>22</v>
       </c>
-      <c r="H1" s="1" t="s">
+      <c r="I1" s="1" t="s">
         <v>23</v>
       </c>
-      <c r="I1" s="1" t="s">
+      <c r="J1" s="1" t="s">
         <v>24</v>
       </c>
-      <c r="J1" s="1" t="s">
+      <c r="K1" s="1" t="s">
         <v>25</v>
       </c>
-      <c r="K1" s="1" t="s">
+      <c r="L1" s="1" t="s">
         <v>26</v>
       </c>
-      <c r="L1" s="1" t="s">
+      <c r="M1" s="1" t="s">
         <v>27</v>
       </c>
     </row>
-    <row r="2" spans="1:12" x14ac:dyDescent="0.45">
+    <row r="2" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A2" s="3">
         <v>4</v>
       </c>
@@ -8072,37 +8288,40 @@
         <v>32</v>
       </c>
       <c r="C2" t="s">
+        <v>14</v>
+      </c>
+      <c r="D2" t="s">
         <v>28</v>
       </c>
-      <c r="D2" t="s">
-        <v>18</v>
-      </c>
-      <c r="E2">
+      <c r="E2" t="s">
+        <v>18</v>
+      </c>
+      <c r="F2">
         <v>80</v>
       </c>
-      <c r="F2">
-        <v>60</v>
-      </c>
       <c r="G2">
+        <v>60</v>
+      </c>
+      <c r="H2">
         <v>40</v>
       </c>
-      <c r="H2">
+      <c r="I2">
         <v>30</v>
       </c>
-      <c r="I2">
-        <v>50</v>
-      </c>
       <c r="J2">
+        <v>50</v>
+      </c>
+      <c r="K2">
         <v>40</v>
       </c>
-      <c r="K2">
+      <c r="L2">
         <v>90</v>
       </c>
-      <c r="L2">
+      <c r="M2">
         <v>40</v>
       </c>
     </row>
-    <row r="3" spans="1:12" x14ac:dyDescent="0.45">
+    <row r="3" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A3" s="3">
         <v>5</v>
       </c>
@@ -8110,37 +8329,40 @@
         <v>32</v>
       </c>
       <c r="C3" t="s">
+        <v>14</v>
+      </c>
+      <c r="D3" t="s">
         <v>28</v>
       </c>
-      <c r="D3" t="s">
-        <v>18</v>
-      </c>
-      <c r="E3">
+      <c r="E3" t="s">
+        <v>18</v>
+      </c>
+      <c r="F3">
         <v>80</v>
       </c>
-      <c r="F3">
+      <c r="G3">
         <v>30</v>
       </c>
-      <c r="G3">
+      <c r="H3">
         <v>40</v>
       </c>
-      <c r="H3">
-        <v>20</v>
-      </c>
       <c r="I3">
+        <v>20</v>
+      </c>
+      <c r="J3">
         <v>40</v>
       </c>
-      <c r="J3">
-        <v>20</v>
-      </c>
       <c r="K3">
-        <v>60</v>
+        <v>20</v>
       </c>
       <c r="L3">
-        <v>50</v>
-      </c>
-    </row>
-    <row r="4" spans="1:12" x14ac:dyDescent="0.45">
+        <v>60</v>
+      </c>
+      <c r="M3">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="4" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A4" s="3">
         <v>6</v>
       </c>
@@ -8148,37 +8370,40 @@
         <v>32</v>
       </c>
       <c r="C4" t="s">
+        <v>13</v>
+      </c>
+      <c r="D4" t="s">
         <v>28</v>
       </c>
-      <c r="D4" t="s">
-        <v>18</v>
-      </c>
-      <c r="E4">
-        <v>60</v>
+      <c r="E4" t="s">
+        <v>18</v>
       </c>
       <c r="F4">
+        <v>60</v>
+      </c>
+      <c r="G4">
         <v>10</v>
       </c>
-      <c r="G4">
-        <v>60</v>
-      </c>
       <c r="H4">
+        <v>60</v>
+      </c>
+      <c r="I4">
         <v>10</v>
       </c>
-      <c r="I4">
-        <v>20</v>
-      </c>
       <c r="J4">
         <v>20</v>
       </c>
       <c r="K4">
+        <v>20</v>
+      </c>
+      <c r="L4">
         <v>30</v>
       </c>
-      <c r="L4">
-        <v>50</v>
-      </c>
-    </row>
-    <row r="5" spans="1:12" x14ac:dyDescent="0.45">
+      <c r="M4">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="5" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A5" s="3">
         <v>7</v>
       </c>
@@ -8186,37 +8411,40 @@
         <v>32</v>
       </c>
       <c r="C5" t="s">
+        <v>13</v>
+      </c>
+      <c r="D5" t="s">
         <v>28</v>
       </c>
-      <c r="D5" t="s">
-        <v>18</v>
-      </c>
-      <c r="E5">
+      <c r="E5" t="s">
+        <v>18</v>
+      </c>
+      <c r="F5">
         <v>70</v>
       </c>
-      <c r="F5">
+      <c r="G5">
         <v>2</v>
       </c>
-      <c r="G5">
+      <c r="H5">
         <v>30</v>
       </c>
-      <c r="H5">
+      <c r="I5">
         <v>35</v>
       </c>
-      <c r="I5">
+      <c r="J5">
         <v>5</v>
       </c>
-      <c r="J5">
+      <c r="K5">
         <v>10</v>
       </c>
-      <c r="K5">
+      <c r="L5">
         <v>40</v>
       </c>
-      <c r="L5">
-        <v>50</v>
-      </c>
-    </row>
-    <row r="6" spans="1:12" x14ac:dyDescent="0.45">
+      <c r="M5">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="6" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A6" s="2">
         <v>10</v>
       </c>
@@ -8224,19 +8452,19 @@
         <v>32</v>
       </c>
       <c r="C6" t="s">
+        <v>13</v>
+      </c>
+      <c r="D6" t="s">
         <v>28</v>
       </c>
-      <c r="D6" t="s">
-        <v>18</v>
-      </c>
-      <c r="E6">
+      <c r="E6" t="s">
+        <v>18</v>
+      </c>
+      <c r="F6">
         <v>6</v>
       </c>
-      <c r="F6">
+      <c r="G6">
         <v>4</v>
-      </c>
-      <c r="G6">
-        <v>5</v>
       </c>
       <c r="H6">
         <v>5</v>
@@ -8245,16 +8473,19 @@
         <v>5</v>
       </c>
       <c r="J6">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="K6">
         <v>3</v>
       </c>
       <c r="L6">
+        <v>3</v>
+      </c>
+      <c r="M6">
         <v>2</v>
       </c>
     </row>
-    <row r="7" spans="1:12" x14ac:dyDescent="0.45">
+    <row r="7" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A7" s="2">
         <v>11</v>
       </c>
@@ -8262,37 +8493,40 @@
         <v>32</v>
       </c>
       <c r="C7" t="s">
+        <v>13</v>
+      </c>
+      <c r="D7" t="s">
         <v>28</v>
       </c>
-      <c r="D7" t="s">
-        <v>18</v>
-      </c>
-      <c r="E7">
+      <c r="E7" t="s">
+        <v>18</v>
+      </c>
+      <c r="F7">
         <v>80</v>
       </c>
-      <c r="F7">
-        <v>20</v>
-      </c>
       <c r="G7">
-        <v>40</v>
+        <v>20</v>
       </c>
       <c r="H7">
         <v>40</v>
       </c>
       <c r="I7">
+        <v>40</v>
+      </c>
+      <c r="J7">
         <v>10</v>
-      </c>
-      <c r="J7">
-        <v>30</v>
       </c>
       <c r="K7">
         <v>30</v>
       </c>
       <c r="L7">
-        <v>50</v>
-      </c>
-    </row>
-    <row r="8" spans="1:12" x14ac:dyDescent="0.45">
+        <v>30</v>
+      </c>
+      <c r="M7">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="8" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A8" s="2">
         <v>12</v>
       </c>
@@ -8300,37 +8534,40 @@
         <v>32</v>
       </c>
       <c r="C8" t="s">
+        <v>13</v>
+      </c>
+      <c r="D8" t="s">
         <v>28</v>
       </c>
-      <c r="D8" t="s">
-        <v>18</v>
-      </c>
-      <c r="E8">
+      <c r="E8" t="s">
+        <v>18</v>
+      </c>
+      <c r="F8">
         <v>95</v>
       </c>
-      <c r="F8">
+      <c r="G8">
         <v>30</v>
       </c>
-      <c r="G8">
-        <v>60</v>
-      </c>
       <c r="H8">
+        <v>60</v>
+      </c>
+      <c r="I8">
         <v>40</v>
       </c>
-      <c r="I8">
+      <c r="J8">
         <v>70</v>
-      </c>
-      <c r="J8">
-        <v>30</v>
       </c>
       <c r="K8">
         <v>30</v>
       </c>
       <c r="L8">
+        <v>30</v>
+      </c>
+      <c r="M8">
         <v>80</v>
       </c>
     </row>
-    <row r="9" spans="1:12" x14ac:dyDescent="0.45">
+    <row r="9" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A9" s="2">
         <v>13</v>
       </c>
@@ -8338,37 +8575,40 @@
         <v>32</v>
       </c>
       <c r="C9" t="s">
+        <v>13</v>
+      </c>
+      <c r="D9" t="s">
         <v>28</v>
       </c>
-      <c r="D9" t="s">
-        <v>18</v>
-      </c>
-      <c r="E9">
+      <c r="E9" t="s">
+        <v>18</v>
+      </c>
+      <c r="F9">
         <v>70</v>
       </c>
-      <c r="F9">
+      <c r="G9">
         <v>30</v>
       </c>
-      <c r="G9">
-        <v>60</v>
-      </c>
       <c r="H9">
-        <v>50</v>
+        <v>60</v>
       </c>
       <c r="I9">
         <v>50</v>
       </c>
       <c r="J9">
+        <v>50</v>
+      </c>
+      <c r="K9">
         <v>10</v>
       </c>
-      <c r="K9">
+      <c r="L9">
         <v>40</v>
       </c>
-      <c r="L9">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="10" spans="1:12" x14ac:dyDescent="0.45">
+      <c r="M9">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="10" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A10" s="2">
         <v>14</v>
       </c>
@@ -8376,37 +8616,40 @@
         <v>32</v>
       </c>
       <c r="C10" t="s">
+        <v>13</v>
+      </c>
+      <c r="D10" t="s">
         <v>28</v>
       </c>
-      <c r="D10" t="s">
-        <v>18</v>
-      </c>
-      <c r="E10">
+      <c r="E10" t="s">
+        <v>18</v>
+      </c>
+      <c r="F10">
         <v>80</v>
       </c>
-      <c r="F10">
-        <v>20</v>
-      </c>
       <c r="G10">
+        <v>20</v>
+      </c>
+      <c r="H10">
         <v>70</v>
       </c>
-      <c r="H10">
-        <v>1</v>
-      </c>
       <c r="I10">
-        <v>60</v>
+        <v>1</v>
       </c>
       <c r="J10">
-        <v>1</v>
+        <v>60</v>
       </c>
       <c r="K10">
+        <v>1</v>
+      </c>
+      <c r="L10">
         <v>10</v>
       </c>
-      <c r="L10">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="11" spans="1:12" x14ac:dyDescent="0.45">
+      <c r="M10">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="11" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A11" s="2">
         <v>15</v>
       </c>
@@ -8414,37 +8657,40 @@
         <v>32</v>
       </c>
       <c r="C11" t="s">
+        <v>13</v>
+      </c>
+      <c r="D11" t="s">
         <v>28</v>
       </c>
-      <c r="D11" t="s">
-        <v>18</v>
-      </c>
-      <c r="E11">
+      <c r="E11" t="s">
+        <v>18</v>
+      </c>
+      <c r="F11">
         <v>80</v>
       </c>
-      <c r="F11">
+      <c r="G11">
         <v>40</v>
       </c>
-      <c r="G11">
+      <c r="H11">
         <v>75</v>
       </c>
-      <c r="H11">
+      <c r="I11">
         <v>40</v>
       </c>
-      <c r="I11">
-        <v>60</v>
-      </c>
       <c r="J11">
+        <v>60</v>
+      </c>
+      <c r="K11">
         <v>10</v>
       </c>
-      <c r="K11">
-        <v>50</v>
-      </c>
       <c r="L11">
+        <v>50</v>
+      </c>
+      <c r="M11">
         <v>55</v>
       </c>
     </row>
-    <row r="12" spans="1:12" x14ac:dyDescent="0.45">
+    <row r="12" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A12" s="2">
         <v>16</v>
       </c>
@@ -8452,37 +8698,40 @@
         <v>32</v>
       </c>
       <c r="C12" t="s">
+        <v>13</v>
+      </c>
+      <c r="D12" t="s">
         <v>28</v>
       </c>
-      <c r="D12" t="s">
-        <v>18</v>
-      </c>
-      <c r="E12">
+      <c r="E12" t="s">
+        <v>18</v>
+      </c>
+      <c r="F12">
         <v>70</v>
       </c>
-      <c r="F12">
-        <v>1</v>
-      </c>
       <c r="G12">
+        <v>1</v>
+      </c>
+      <c r="H12">
         <v>40</v>
       </c>
-      <c r="H12">
+      <c r="I12">
         <v>80</v>
       </c>
-      <c r="I12">
+      <c r="J12">
         <v>5</v>
       </c>
-      <c r="J12">
-        <v>60</v>
-      </c>
       <c r="K12">
+        <v>60</v>
+      </c>
+      <c r="L12">
         <v>70</v>
       </c>
-      <c r="L12">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="13" spans="1:12" x14ac:dyDescent="0.45">
+      <c r="M12">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="13" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A13" s="2">
         <v>17</v>
       </c>
@@ -8490,34 +8739,37 @@
         <v>32</v>
       </c>
       <c r="C13" t="s">
+        <v>13</v>
+      </c>
+      <c r="D13" t="s">
         <v>28</v>
       </c>
-      <c r="D13" t="s">
-        <v>18</v>
-      </c>
-      <c r="E13">
-        <v>50</v>
+      <c r="E13" t="s">
+        <v>18</v>
       </c>
       <c r="F13">
-        <v>60</v>
+        <v>50</v>
       </c>
       <c r="G13">
+        <v>60</v>
+      </c>
+      <c r="H13">
         <v>90</v>
       </c>
-      <c r="H13">
-        <v>1</v>
-      </c>
       <c r="I13">
+        <v>1</v>
+      </c>
+      <c r="J13">
         <v>70</v>
       </c>
-      <c r="K13">
-        <v>1</v>
-      </c>
       <c r="L13">
+        <v>1</v>
+      </c>
+      <c r="M13">
         <v>80</v>
       </c>
     </row>
-    <row r="14" spans="1:12" x14ac:dyDescent="0.45">
+    <row r="14" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A14" s="2">
         <v>18</v>
       </c>
@@ -8525,37 +8777,40 @@
         <v>32</v>
       </c>
       <c r="C14" t="s">
+        <v>13</v>
+      </c>
+      <c r="D14" t="s">
         <v>28</v>
       </c>
-      <c r="D14" t="s">
-        <v>18</v>
-      </c>
-      <c r="E14">
-        <v>60</v>
+      <c r="E14" t="s">
+        <v>18</v>
       </c>
       <c r="F14">
+        <v>60</v>
+      </c>
+      <c r="G14">
         <v>30</v>
       </c>
-      <c r="G14">
+      <c r="H14">
         <v>90</v>
       </c>
-      <c r="H14">
+      <c r="I14">
         <v>10</v>
       </c>
-      <c r="I14">
+      <c r="J14">
         <v>90</v>
       </c>
-      <c r="J14">
+      <c r="K14">
         <v>40</v>
-      </c>
-      <c r="K14">
-        <v>10</v>
       </c>
       <c r="L14">
         <v>10</v>
       </c>
-    </row>
-    <row r="15" spans="1:12" x14ac:dyDescent="0.45">
+      <c r="M14">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="15" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A15" s="2">
         <v>19</v>
       </c>
@@ -8566,48 +8821,51 @@
         <v>13</v>
       </c>
       <c r="D15" t="s">
-        <v>18</v>
-      </c>
-      <c r="E15">
+        <v>13</v>
+      </c>
+      <c r="E15" t="s">
+        <v>18</v>
+      </c>
+      <c r="F15">
         <v>70</v>
       </c>
-      <c r="F15">
-        <v>20</v>
-      </c>
       <c r="G15">
-        <v>1</v>
+        <v>20</v>
       </c>
       <c r="H15">
-        <v>50</v>
+        <v>1</v>
       </c>
       <c r="I15">
+        <v>50</v>
+      </c>
+      <c r="J15">
         <v>40</v>
       </c>
-      <c r="J15">
-        <v>50</v>
-      </c>
       <c r="K15">
-        <v>60</v>
+        <v>50</v>
       </c>
       <c r="L15">
-        <v>50</v>
-      </c>
-    </row>
-    <row r="16" spans="1:12" x14ac:dyDescent="0.45">
+        <v>60</v>
+      </c>
+      <c r="M15">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="16" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A16" s="2">
         <v>20</v>
       </c>
       <c r="B16" s="4" t="s">
         <v>32</v>
       </c>
-      <c r="C16" s="4" t="s">
+      <c r="C16" t="s">
+        <v>14</v>
+      </c>
+      <c r="D16" s="4" t="s">
         <v>28</v>
       </c>
-      <c r="D16" t="s">
-        <v>18</v>
-      </c>
-      <c r="E16">
-        <v>40</v>
+      <c r="E16" t="s">
+        <v>18</v>
       </c>
       <c r="F16">
         <v>40</v>
@@ -8616,22 +8874,25 @@
         <v>40</v>
       </c>
       <c r="H16">
-        <v>60</v>
+        <v>40</v>
       </c>
       <c r="I16">
         <v>60</v>
       </c>
       <c r="J16">
-        <v>50</v>
+        <v>60</v>
       </c>
       <c r="K16">
+        <v>50</v>
+      </c>
+      <c r="L16">
         <v>30</v>
       </c>
-      <c r="L16">
-        <v>50</v>
-      </c>
-    </row>
-    <row r="17" spans="1:12" x14ac:dyDescent="0.45">
+      <c r="M16">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="17" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A17" s="2">
         <v>21</v>
       </c>
@@ -8639,37 +8900,40 @@
         <v>32</v>
       </c>
       <c r="C17" t="s">
+        <v>13</v>
+      </c>
+      <c r="D17" t="s">
         <v>28</v>
       </c>
-      <c r="D17" t="s">
-        <v>18</v>
-      </c>
-      <c r="E17">
+      <c r="E17" t="s">
+        <v>18</v>
+      </c>
+      <c r="F17">
         <v>80</v>
       </c>
-      <c r="F17">
-        <v>20</v>
-      </c>
       <c r="G17">
+        <v>20</v>
+      </c>
+      <c r="H17">
         <v>70</v>
       </c>
-      <c r="H17">
-        <v>20</v>
-      </c>
       <c r="I17">
+        <v>20</v>
+      </c>
+      <c r="J17">
         <v>40</v>
       </c>
-      <c r="J17">
-        <v>20</v>
-      </c>
       <c r="K17">
-        <v>50</v>
+        <v>20</v>
       </c>
       <c r="L17">
+        <v>50</v>
+      </c>
+      <c r="M17">
         <v>45</v>
       </c>
     </row>
-    <row r="18" spans="1:12" x14ac:dyDescent="0.45">
+    <row r="18" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A18" s="2">
         <v>22</v>
       </c>
@@ -8677,37 +8941,40 @@
         <v>32</v>
       </c>
       <c r="C18" t="s">
+        <v>14</v>
+      </c>
+      <c r="D18" t="s">
         <v>28</v>
       </c>
-      <c r="D18" t="s">
+      <c r="E18" t="s">
         <v>17</v>
       </c>
-      <c r="E18">
+      <c r="F18">
         <v>40</v>
       </c>
-      <c r="F18">
-        <v>1</v>
-      </c>
       <c r="G18">
+        <v>1</v>
+      </c>
+      <c r="H18">
         <v>90</v>
       </c>
-      <c r="H18">
-        <v>60</v>
-      </c>
       <c r="I18">
-        <v>50</v>
+        <v>60</v>
       </c>
       <c r="J18">
         <v>50</v>
       </c>
       <c r="K18">
+        <v>50</v>
+      </c>
+      <c r="L18">
         <v>70</v>
       </c>
-      <c r="L18">
+      <c r="M18">
         <v>80</v>
       </c>
     </row>
-    <row r="19" spans="1:12" x14ac:dyDescent="0.45">
+    <row r="19" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A19" s="2">
         <v>23</v>
       </c>
@@ -8715,37 +8982,40 @@
         <v>32</v>
       </c>
       <c r="C19" t="s">
+        <v>13</v>
+      </c>
+      <c r="D19" t="s">
         <v>28</v>
       </c>
-      <c r="D19" t="s">
-        <v>18</v>
-      </c>
-      <c r="E19">
-        <v>20</v>
+      <c r="E19" t="s">
+        <v>18</v>
       </c>
       <c r="F19">
+        <v>20</v>
+      </c>
+      <c r="G19">
         <v>40</v>
-      </c>
-      <c r="G19">
-        <v>90</v>
       </c>
       <c r="H19">
         <v>90</v>
       </c>
       <c r="I19">
-        <v>60</v>
+        <v>90</v>
       </c>
       <c r="J19">
-        <v>50</v>
+        <v>60</v>
       </c>
       <c r="K19">
+        <v>50</v>
+      </c>
+      <c r="L19">
         <v>10</v>
       </c>
-      <c r="L19">
-        <v>50</v>
-      </c>
-    </row>
-    <row r="20" spans="1:12" x14ac:dyDescent="0.45">
+      <c r="M19">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="20" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A20" s="2">
         <v>24</v>
       </c>
@@ -8753,37 +9023,40 @@
         <v>32</v>
       </c>
       <c r="C20" t="s">
+        <v>13</v>
+      </c>
+      <c r="D20" t="s">
         <v>28</v>
       </c>
-      <c r="D20" t="s">
-        <v>18</v>
-      </c>
-      <c r="E20">
+      <c r="E20" t="s">
+        <v>18</v>
+      </c>
+      <c r="F20">
         <v>90</v>
       </c>
-      <c r="F20">
-        <v>1</v>
-      </c>
       <c r="G20">
+        <v>1</v>
+      </c>
+      <c r="H20">
         <v>40</v>
       </c>
-      <c r="H20">
+      <c r="I20">
         <v>30</v>
       </c>
-      <c r="I20">
-        <v>1</v>
-      </c>
       <c r="J20">
+        <v>1</v>
+      </c>
+      <c r="K20">
         <v>40</v>
       </c>
-      <c r="K20">
-        <v>1</v>
-      </c>
       <c r="L20">
+        <v>1</v>
+      </c>
+      <c r="M20">
         <v>40</v>
       </c>
     </row>
-    <row r="21" spans="1:12" x14ac:dyDescent="0.45">
+    <row r="21" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A21" s="2">
         <v>25</v>
       </c>
@@ -8791,34 +9064,37 @@
         <v>32</v>
       </c>
       <c r="C21" t="s">
+        <v>14</v>
+      </c>
+      <c r="D21" t="s">
         <v>28</v>
       </c>
-      <c r="D21" t="s">
-        <v>18</v>
-      </c>
-      <c r="E21">
-        <v>60</v>
+      <c r="E21" t="s">
+        <v>18</v>
       </c>
       <c r="F21">
+        <v>60</v>
+      </c>
+      <c r="G21">
         <v>30</v>
       </c>
-      <c r="G21">
+      <c r="H21">
         <v>100</v>
       </c>
-      <c r="H21">
+      <c r="I21">
         <v>40</v>
       </c>
-      <c r="I21">
+      <c r="J21">
         <v>30</v>
       </c>
-      <c r="K21">
-        <v>60</v>
-      </c>
       <c r="L21">
+        <v>60</v>
+      </c>
+      <c r="M21">
         <v>80</v>
       </c>
     </row>
-    <row r="22" spans="1:12" x14ac:dyDescent="0.45">
+    <row r="22" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A22" s="2">
         <v>26</v>
       </c>
@@ -8826,13 +9102,13 @@
         <v>32</v>
       </c>
       <c r="C22" t="s">
+        <v>13</v>
+      </c>
+      <c r="D22" t="s">
         <v>28</v>
       </c>
-      <c r="D22" t="s">
-        <v>18</v>
-      </c>
-      <c r="E22">
-        <v>50</v>
+      <c r="E22" t="s">
+        <v>18</v>
       </c>
       <c r="F22">
         <v>50</v>
@@ -8841,10 +9117,10 @@
         <v>50</v>
       </c>
       <c r="H22">
-        <v>20</v>
+        <v>50</v>
       </c>
       <c r="I22">
-        <v>50</v>
+        <v>20</v>
       </c>
       <c r="J22">
         <v>50</v>
@@ -8853,10 +9129,13 @@
         <v>50</v>
       </c>
       <c r="L22">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="23" spans="1:12" x14ac:dyDescent="0.45">
+        <v>50</v>
+      </c>
+      <c r="M22">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="23" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A23" s="2">
         <v>27</v>
       </c>
@@ -8864,37 +9143,40 @@
         <v>32</v>
       </c>
       <c r="C23" t="s">
+        <v>13</v>
+      </c>
+      <c r="D23" t="s">
         <v>28</v>
       </c>
-      <c r="D23" t="s">
-        <v>18</v>
-      </c>
-      <c r="E23">
+      <c r="E23" t="s">
+        <v>18</v>
+      </c>
+      <c r="F23">
         <v>90</v>
       </c>
-      <c r="F23">
+      <c r="G23">
         <v>10</v>
       </c>
-      <c r="G23">
+      <c r="H23">
         <v>90</v>
       </c>
-      <c r="H23">
+      <c r="I23">
         <v>5</v>
       </c>
-      <c r="I23">
+      <c r="J23">
         <v>80</v>
       </c>
-      <c r="J23">
+      <c r="K23">
         <v>5</v>
       </c>
-      <c r="K23">
-        <v>1</v>
-      </c>
       <c r="L23">
+        <v>1</v>
+      </c>
+      <c r="M23">
         <v>85</v>
       </c>
     </row>
-    <row r="24" spans="1:12" x14ac:dyDescent="0.45">
+    <row r="24" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A24" s="2">
         <v>29</v>
       </c>
@@ -8902,37 +9184,40 @@
         <v>32</v>
       </c>
       <c r="C24" t="s">
+        <v>14</v>
+      </c>
+      <c r="D24" t="s">
         <v>28</v>
       </c>
-      <c r="D24" t="s">
-        <v>18</v>
-      </c>
-      <c r="E24">
+      <c r="E24" t="s">
+        <v>18</v>
+      </c>
+      <c r="F24">
         <v>75</v>
       </c>
-      <c r="F24">
+      <c r="G24">
         <v>4</v>
       </c>
-      <c r="G24">
+      <c r="H24">
         <v>92</v>
       </c>
-      <c r="H24">
+      <c r="I24">
         <v>2</v>
       </c>
-      <c r="I24">
+      <c r="J24">
         <v>10</v>
       </c>
-      <c r="J24">
-        <v>60</v>
-      </c>
       <c r="K24">
         <v>60</v>
       </c>
       <c r="L24">
         <v>60</v>
       </c>
-    </row>
-    <row r="25" spans="1:12" x14ac:dyDescent="0.45">
+      <c r="M24">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="25" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A25" s="2">
         <v>30</v>
       </c>
@@ -8940,37 +9225,40 @@
         <v>32</v>
       </c>
       <c r="C25" t="s">
+        <v>13</v>
+      </c>
+      <c r="D25" t="s">
         <v>28</v>
       </c>
-      <c r="D25" t="s">
-        <v>18</v>
-      </c>
-      <c r="E25">
+      <c r="E25" t="s">
+        <v>18</v>
+      </c>
+      <c r="F25">
         <v>77</v>
       </c>
-      <c r="F25">
+      <c r="G25">
         <v>22</v>
       </c>
-      <c r="G25">
+      <c r="H25">
         <v>44</v>
       </c>
-      <c r="H25">
+      <c r="I25">
         <v>34</v>
       </c>
-      <c r="I25">
+      <c r="J25">
         <v>32</v>
       </c>
-      <c r="J25">
+      <c r="K25">
         <v>66</v>
       </c>
-      <c r="K25">
+      <c r="L25">
         <v>24</v>
       </c>
-      <c r="L25">
+      <c r="M25">
         <v>12</v>
       </c>
     </row>
-    <row r="26" spans="1:12" x14ac:dyDescent="0.45">
+    <row r="26" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A26" s="2">
         <v>31</v>
       </c>
@@ -8978,34 +9266,37 @@
         <v>32</v>
       </c>
       <c r="C26" t="s">
+        <v>14</v>
+      </c>
+      <c r="D26" t="s">
         <v>28</v>
       </c>
-      <c r="D26" t="s">
-        <v>18</v>
-      </c>
-      <c r="E26">
+      <c r="E26" t="s">
+        <v>18</v>
+      </c>
+      <c r="F26">
         <v>88</v>
       </c>
-      <c r="F26">
+      <c r="G26">
         <v>30</v>
       </c>
-      <c r="G26">
+      <c r="H26">
         <v>90</v>
       </c>
-      <c r="H26">
+      <c r="I26">
         <v>2</v>
       </c>
-      <c r="I26">
+      <c r="J26">
         <v>80</v>
       </c>
-      <c r="K26">
+      <c r="L26">
         <v>2</v>
       </c>
-      <c r="L26">
+      <c r="M26">
         <v>90</v>
       </c>
     </row>
-    <row r="27" spans="1:12" x14ac:dyDescent="0.45">
+    <row r="27" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A27" s="2">
         <v>32</v>
       </c>
@@ -9013,37 +9304,40 @@
         <v>32</v>
       </c>
       <c r="C27" t="s">
+        <v>14</v>
+      </c>
+      <c r="D27" t="s">
         <v>28</v>
       </c>
-      <c r="D27" t="s">
-        <v>18</v>
-      </c>
-      <c r="E27">
-        <v>50</v>
+      <c r="E27" t="s">
+        <v>18</v>
       </c>
       <c r="F27">
-        <v>20</v>
+        <v>50</v>
       </c>
       <c r="G27">
+        <v>20</v>
+      </c>
+      <c r="H27">
         <v>30</v>
       </c>
-      <c r="H27">
+      <c r="I27">
         <v>40</v>
       </c>
-      <c r="I27">
-        <v>1</v>
-      </c>
       <c r="J27">
+        <v>1</v>
+      </c>
+      <c r="K27">
         <v>30</v>
       </c>
-      <c r="K27">
-        <v>50</v>
-      </c>
       <c r="L27">
+        <v>50</v>
+      </c>
+      <c r="M27">
         <v>40</v>
       </c>
     </row>
-    <row r="28" spans="1:12" x14ac:dyDescent="0.45">
+    <row r="28" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A28" s="2">
         <v>33</v>
       </c>
@@ -9051,37 +9345,40 @@
         <v>32</v>
       </c>
       <c r="C28" t="s">
+        <v>13</v>
+      </c>
+      <c r="D28" t="s">
         <v>28</v>
       </c>
-      <c r="D28" t="s">
-        <v>18</v>
-      </c>
-      <c r="E28">
+      <c r="E28" t="s">
+        <v>18</v>
+      </c>
+      <c r="F28">
         <v>90</v>
       </c>
-      <c r="F28">
-        <v>1</v>
-      </c>
       <c r="G28">
+        <v>1</v>
+      </c>
+      <c r="H28">
         <v>80</v>
       </c>
-      <c r="H28">
-        <v>1</v>
-      </c>
       <c r="I28">
-        <v>20</v>
+        <v>1</v>
       </c>
       <c r="J28">
-        <v>1</v>
+        <v>20</v>
       </c>
       <c r="K28">
+        <v>1</v>
+      </c>
+      <c r="L28">
         <v>10</v>
       </c>
-      <c r="L28">
+      <c r="M28">
         <v>70</v>
       </c>
     </row>
-    <row r="29" spans="1:12" x14ac:dyDescent="0.45">
+    <row r="29" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A29" s="2">
         <v>34</v>
       </c>
@@ -9089,37 +9386,40 @@
         <v>32</v>
       </c>
       <c r="C29" t="s">
+        <v>13</v>
+      </c>
+      <c r="D29" t="s">
         <v>28</v>
       </c>
-      <c r="D29" t="s">
-        <v>18</v>
-      </c>
-      <c r="E29">
+      <c r="E29" t="s">
+        <v>18</v>
+      </c>
+      <c r="F29">
         <v>40</v>
       </c>
-      <c r="F29">
-        <v>20</v>
-      </c>
       <c r="G29">
-        <v>50</v>
+        <v>20</v>
       </c>
       <c r="H29">
+        <v>50</v>
+      </c>
+      <c r="I29">
         <v>30</v>
       </c>
-      <c r="I29">
+      <c r="J29">
         <v>40</v>
       </c>
-      <c r="J29">
-        <v>1</v>
-      </c>
       <c r="K29">
         <v>1</v>
       </c>
       <c r="L29">
+        <v>1</v>
+      </c>
+      <c r="M29">
         <v>40</v>
       </c>
     </row>
-    <row r="30" spans="1:12" x14ac:dyDescent="0.45">
+    <row r="30" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A30" s="2">
         <v>35</v>
       </c>
@@ -9127,37 +9427,40 @@
         <v>32</v>
       </c>
       <c r="C30" t="s">
+        <v>13</v>
+      </c>
+      <c r="D30" t="s">
         <v>28</v>
       </c>
-      <c r="D30" t="s">
-        <v>18</v>
-      </c>
-      <c r="E30">
+      <c r="E30" t="s">
+        <v>18</v>
+      </c>
+      <c r="F30">
         <v>100</v>
       </c>
-      <c r="F30">
-        <v>1</v>
-      </c>
       <c r="G30">
-        <v>50</v>
+        <v>1</v>
       </c>
       <c r="H30">
-        <v>60</v>
+        <v>50</v>
       </c>
       <c r="I30">
+        <v>60</v>
+      </c>
+      <c r="J30">
         <v>10</v>
       </c>
-      <c r="J30">
-        <v>1</v>
-      </c>
       <c r="K30">
+        <v>1</v>
+      </c>
+      <c r="L30">
         <v>5</v>
       </c>
-      <c r="L30">
+      <c r="M30">
         <v>40</v>
       </c>
     </row>
-    <row r="31" spans="1:12" x14ac:dyDescent="0.45">
+    <row r="31" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A31" s="2">
         <v>36</v>
       </c>
@@ -9165,37 +9468,40 @@
         <v>32</v>
       </c>
       <c r="C31" t="s">
+        <v>13</v>
+      </c>
+      <c r="D31" t="s">
         <v>28</v>
       </c>
-      <c r="D31" t="s">
-        <v>18</v>
-      </c>
-      <c r="E31">
+      <c r="E31" t="s">
+        <v>18</v>
+      </c>
+      <c r="F31">
         <v>65</v>
       </c>
-      <c r="F31">
+      <c r="G31">
         <v>40</v>
       </c>
-      <c r="G31">
+      <c r="H31">
         <v>70</v>
       </c>
-      <c r="H31">
-        <v>50</v>
-      </c>
       <c r="I31">
-        <v>20</v>
+        <v>50</v>
       </c>
       <c r="J31">
-        <v>50</v>
+        <v>20</v>
       </c>
       <c r="K31">
+        <v>50</v>
+      </c>
+      <c r="L31">
         <v>30</v>
       </c>
-      <c r="L31">
+      <c r="M31">
         <v>70</v>
       </c>
     </row>
-    <row r="32" spans="1:12" x14ac:dyDescent="0.45">
+    <row r="32" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A32" s="2">
         <v>37</v>
       </c>
@@ -9203,31 +9509,34 @@
         <v>32</v>
       </c>
       <c r="C32" t="s">
+        <v>13</v>
+      </c>
+      <c r="D32" t="s">
         <v>28</v>
       </c>
-      <c r="D32" t="s">
-        <v>18</v>
-      </c>
-      <c r="E32">
-        <v>70</v>
+      <c r="E32" t="s">
+        <v>18</v>
       </c>
       <c r="F32">
         <v>70</v>
       </c>
       <c r="G32">
+        <v>70</v>
+      </c>
+      <c r="H32">
         <v>8</v>
       </c>
-      <c r="I32">
+      <c r="J32">
         <v>7</v>
       </c>
-      <c r="J32">
-        <v>20</v>
-      </c>
-      <c r="L32">
-        <v>50</v>
-      </c>
-    </row>
-    <row r="33" spans="1:12" x14ac:dyDescent="0.45">
+      <c r="K32">
+        <v>20</v>
+      </c>
+      <c r="M32">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="33" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A33" s="2">
         <v>38</v>
       </c>
@@ -9235,37 +9544,40 @@
         <v>32</v>
       </c>
       <c r="C33" t="s">
+        <v>13</v>
+      </c>
+      <c r="D33" t="s">
         <v>28</v>
       </c>
-      <c r="D33" t="s">
-        <v>18</v>
-      </c>
-      <c r="E33">
+      <c r="E33" t="s">
+        <v>18</v>
+      </c>
+      <c r="F33">
         <v>80</v>
       </c>
-      <c r="F33">
-        <v>1</v>
-      </c>
       <c r="G33">
+        <v>1</v>
+      </c>
+      <c r="H33">
         <v>30</v>
       </c>
-      <c r="H33">
-        <v>50</v>
-      </c>
       <c r="I33">
-        <v>1</v>
+        <v>50</v>
       </c>
       <c r="J33">
-        <v>50</v>
+        <v>1</v>
       </c>
       <c r="K33">
-        <v>60</v>
+        <v>50</v>
       </c>
       <c r="L33">
+        <v>60</v>
+      </c>
+      <c r="M33">
         <v>3</v>
       </c>
     </row>
-    <row r="34" spans="1:12" x14ac:dyDescent="0.45">
+    <row r="34" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A34" s="2">
         <v>39</v>
       </c>
@@ -9273,37 +9585,40 @@
         <v>32</v>
       </c>
       <c r="C34" t="s">
+        <v>13</v>
+      </c>
+      <c r="D34" t="s">
         <v>28</v>
       </c>
-      <c r="D34" t="s">
-        <v>18</v>
-      </c>
-      <c r="E34">
+      <c r="E34" t="s">
+        <v>18</v>
+      </c>
+      <c r="F34">
         <v>70</v>
       </c>
-      <c r="F34">
+      <c r="G34">
         <v>40</v>
       </c>
-      <c r="G34">
+      <c r="H34">
         <v>65</v>
       </c>
-      <c r="H34">
+      <c r="I34">
         <v>40</v>
       </c>
-      <c r="I34">
+      <c r="J34">
         <v>55</v>
       </c>
-      <c r="J34">
+      <c r="K34">
         <v>40</v>
       </c>
-      <c r="K34">
-        <v>50</v>
-      </c>
       <c r="L34">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="35" spans="1:12" x14ac:dyDescent="0.45">
+        <v>50</v>
+      </c>
+      <c r="M34">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="35" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A35" s="2">
         <v>40</v>
       </c>
@@ -9311,37 +9626,40 @@
         <v>32</v>
       </c>
       <c r="C35" t="s">
+        <v>13</v>
+      </c>
+      <c r="D35" t="s">
         <v>28</v>
       </c>
-      <c r="D35" t="s">
-        <v>18</v>
-      </c>
-      <c r="E35">
+      <c r="E35" t="s">
+        <v>18</v>
+      </c>
+      <c r="F35">
         <v>80</v>
       </c>
-      <c r="F35">
+      <c r="G35">
         <v>55</v>
       </c>
-      <c r="G35">
+      <c r="H35">
         <v>75</v>
       </c>
-      <c r="H35">
-        <v>50</v>
-      </c>
       <c r="I35">
+        <v>50</v>
+      </c>
+      <c r="J35">
         <v>55</v>
       </c>
-      <c r="J35">
-        <v>50</v>
-      </c>
       <c r="K35">
+        <v>50</v>
+      </c>
+      <c r="L35">
         <v>45</v>
       </c>
-      <c r="L35">
+      <c r="M35">
         <v>80</v>
       </c>
     </row>
-    <row r="36" spans="1:12" x14ac:dyDescent="0.45">
+    <row r="36" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A36" s="2">
         <v>41</v>
       </c>
@@ -9349,37 +9667,40 @@
         <v>32</v>
       </c>
       <c r="C36" t="s">
+        <v>14</v>
+      </c>
+      <c r="D36" t="s">
         <v>28</v>
       </c>
-      <c r="D36" t="s">
-        <v>18</v>
-      </c>
-      <c r="E36">
+      <c r="E36" t="s">
+        <v>18</v>
+      </c>
+      <c r="F36">
         <v>90</v>
-      </c>
-      <c r="F36">
-        <v>100</v>
       </c>
       <c r="G36">
         <v>100</v>
       </c>
       <c r="H36">
-        <v>1</v>
+        <v>100</v>
       </c>
       <c r="I36">
-        <v>50</v>
+        <v>1</v>
       </c>
       <c r="J36">
-        <v>1</v>
+        <v>50</v>
       </c>
       <c r="K36">
         <v>1</v>
       </c>
       <c r="L36">
+        <v>1</v>
+      </c>
+      <c r="M36">
         <v>90</v>
       </c>
     </row>
-    <row r="37" spans="1:12" x14ac:dyDescent="0.45">
+    <row r="37" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A37" s="2">
         <v>42</v>
       </c>
@@ -9387,37 +9708,40 @@
         <v>32</v>
       </c>
       <c r="C37" t="s">
+        <v>14</v>
+      </c>
+      <c r="D37" t="s">
         <v>28</v>
       </c>
-      <c r="D37" t="s">
-        <v>18</v>
-      </c>
-      <c r="E37">
+      <c r="E37" t="s">
+        <v>18</v>
+      </c>
+      <c r="F37">
         <v>85</v>
       </c>
-      <c r="F37">
+      <c r="G37">
         <v>10</v>
       </c>
-      <c r="G37">
-        <v>50</v>
-      </c>
       <c r="H37">
+        <v>50</v>
+      </c>
+      <c r="I37">
         <v>30</v>
       </c>
-      <c r="I37">
+      <c r="J37">
         <v>15</v>
       </c>
-      <c r="J37">
+      <c r="K37">
         <v>30</v>
       </c>
-      <c r="K37">
+      <c r="L37">
         <v>75</v>
       </c>
-      <c r="L37">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="38" spans="1:12" x14ac:dyDescent="0.45">
+      <c r="M37">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="38" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A38" s="2">
         <v>43</v>
       </c>
@@ -9425,37 +9749,40 @@
         <v>32</v>
       </c>
       <c r="C38" t="s">
+        <v>13</v>
+      </c>
+      <c r="D38" t="s">
         <v>28</v>
       </c>
-      <c r="D38" t="s">
-        <v>18</v>
-      </c>
-      <c r="E38">
+      <c r="E38" t="s">
+        <v>18</v>
+      </c>
+      <c r="F38">
         <v>40</v>
       </c>
-      <c r="F38">
-        <v>1</v>
-      </c>
       <c r="G38">
+        <v>1</v>
+      </c>
+      <c r="H38">
         <v>80</v>
       </c>
-      <c r="H38">
+      <c r="I38">
         <v>30</v>
       </c>
-      <c r="I38">
+      <c r="J38">
         <v>2</v>
       </c>
-      <c r="J38">
+      <c r="K38">
         <v>70</v>
       </c>
-      <c r="K38">
-        <v>50</v>
-      </c>
       <c r="L38">
+        <v>50</v>
+      </c>
+      <c r="M38">
         <v>30</v>
       </c>
     </row>
-    <row r="39" spans="1:12" x14ac:dyDescent="0.45">
+    <row r="39" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A39" s="2">
         <v>44</v>
       </c>
@@ -9463,37 +9790,40 @@
         <v>32</v>
       </c>
       <c r="C39" t="s">
+        <v>13</v>
+      </c>
+      <c r="D39" t="s">
         <v>28</v>
       </c>
-      <c r="D39" t="s">
-        <v>18</v>
-      </c>
-      <c r="E39">
+      <c r="E39" t="s">
+        <v>18</v>
+      </c>
+      <c r="F39">
         <v>70</v>
       </c>
-      <c r="F39">
-        <v>1</v>
-      </c>
       <c r="G39">
-        <v>60</v>
+        <v>1</v>
       </c>
       <c r="H39">
+        <v>60</v>
+      </c>
+      <c r="I39">
         <v>30</v>
       </c>
-      <c r="I39">
-        <v>1</v>
-      </c>
       <c r="J39">
-        <v>60</v>
+        <v>1</v>
       </c>
       <c r="K39">
         <v>60</v>
       </c>
       <c r="L39">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="40" spans="1:12" x14ac:dyDescent="0.45">
+        <v>60</v>
+      </c>
+      <c r="M39">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="40" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A40" s="2">
         <v>45</v>
       </c>
@@ -9501,37 +9831,40 @@
         <v>32</v>
       </c>
       <c r="C40" t="s">
+        <v>13</v>
+      </c>
+      <c r="D40" t="s">
         <v>28</v>
       </c>
-      <c r="D40" t="s">
+      <c r="E40" t="s">
         <v>17</v>
       </c>
-      <c r="E40">
+      <c r="F40">
         <v>90</v>
       </c>
-      <c r="F40">
+      <c r="G40">
         <v>10</v>
       </c>
-      <c r="G40">
-        <v>60</v>
-      </c>
       <c r="H40">
+        <v>60</v>
+      </c>
+      <c r="I40">
         <v>10</v>
       </c>
-      <c r="I40">
+      <c r="J40">
         <v>40</v>
       </c>
-      <c r="J40">
-        <v>50</v>
-      </c>
       <c r="K40">
+        <v>50</v>
+      </c>
+      <c r="L40">
         <v>10</v>
       </c>
-      <c r="L40">
+      <c r="M40">
         <v>80</v>
       </c>
     </row>
-    <row r="41" spans="1:12" x14ac:dyDescent="0.45">
+    <row r="41" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A41" s="2">
         <v>46</v>
       </c>
@@ -9539,37 +9872,40 @@
         <v>32</v>
       </c>
       <c r="C41" t="s">
+        <v>13</v>
+      </c>
+      <c r="D41" t="s">
         <v>28</v>
       </c>
-      <c r="D41" t="s">
-        <v>18</v>
-      </c>
-      <c r="E41">
+      <c r="E41" t="s">
+        <v>18</v>
+      </c>
+      <c r="F41">
         <v>70</v>
       </c>
-      <c r="F41">
-        <v>20</v>
-      </c>
       <c r="G41">
-        <v>60</v>
+        <v>20</v>
       </c>
       <c r="H41">
-        <v>20</v>
+        <v>60</v>
       </c>
       <c r="I41">
-        <v>1</v>
+        <v>20</v>
       </c>
       <c r="J41">
+        <v>1</v>
+      </c>
+      <c r="K41">
         <v>10</v>
       </c>
-      <c r="K41">
+      <c r="L41">
         <v>40</v>
       </c>
-      <c r="L41">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="42" spans="1:12" x14ac:dyDescent="0.45">
+      <c r="M41">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="42" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A42" s="2">
         <v>47</v>
       </c>
@@ -9577,37 +9913,40 @@
         <v>32</v>
       </c>
       <c r="C42" t="s">
+        <v>13</v>
+      </c>
+      <c r="D42" t="s">
         <v>28</v>
       </c>
-      <c r="D42" t="s">
-        <v>18</v>
-      </c>
-      <c r="E42">
+      <c r="E42" t="s">
+        <v>18</v>
+      </c>
+      <c r="F42">
         <v>90</v>
       </c>
-      <c r="F42">
-        <v>50</v>
-      </c>
       <c r="G42">
+        <v>50</v>
+      </c>
+      <c r="H42">
         <v>100</v>
       </c>
-      <c r="H42">
-        <v>1</v>
-      </c>
       <c r="I42">
-        <v>60</v>
+        <v>1</v>
       </c>
       <c r="J42">
-        <v>1</v>
+        <v>60</v>
       </c>
       <c r="K42">
         <v>1</v>
       </c>
       <c r="L42">
+        <v>1</v>
+      </c>
+      <c r="M42">
         <v>90</v>
       </c>
     </row>
-    <row r="43" spans="1:12" x14ac:dyDescent="0.45">
+    <row r="43" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A43" s="2">
         <v>48</v>
       </c>
@@ -9615,37 +9954,40 @@
         <v>32</v>
       </c>
       <c r="C43" t="s">
+        <v>13</v>
+      </c>
+      <c r="D43" t="s">
         <v>28</v>
       </c>
-      <c r="D43" t="s">
-        <v>18</v>
-      </c>
-      <c r="E43">
+      <c r="E43" t="s">
+        <v>18</v>
+      </c>
+      <c r="F43">
         <v>40</v>
       </c>
-      <c r="F43">
-        <v>1</v>
-      </c>
       <c r="G43">
-        <v>50</v>
+        <v>1</v>
       </c>
       <c r="H43">
+        <v>50</v>
+      </c>
+      <c r="I43">
         <v>100</v>
       </c>
-      <c r="I43">
-        <v>1</v>
-      </c>
       <c r="J43">
-        <v>100</v>
+        <v>1</v>
       </c>
       <c r="K43">
         <v>100</v>
       </c>
       <c r="L43">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="44" spans="1:12" x14ac:dyDescent="0.45">
+        <v>100</v>
+      </c>
+      <c r="M43">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="44" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A44" s="2">
         <v>49</v>
       </c>
@@ -9653,37 +9995,40 @@
         <v>32</v>
       </c>
       <c r="C44" t="s">
+        <v>13</v>
+      </c>
+      <c r="D44" t="s">
         <v>28</v>
       </c>
-      <c r="D44" t="s">
-        <v>18</v>
-      </c>
-      <c r="E44">
+      <c r="E44" t="s">
+        <v>18</v>
+      </c>
+      <c r="F44">
         <v>90</v>
       </c>
-      <c r="F44">
-        <v>1</v>
-      </c>
       <c r="G44">
-        <v>50</v>
+        <v>1</v>
       </c>
       <c r="H44">
+        <v>50</v>
+      </c>
+      <c r="I44">
         <v>30</v>
       </c>
-      <c r="I44">
-        <v>1</v>
-      </c>
       <c r="J44">
+        <v>1</v>
+      </c>
+      <c r="K44">
         <v>10</v>
-      </c>
-      <c r="K44">
-        <v>80</v>
       </c>
       <c r="L44">
         <v>80</v>
       </c>
-    </row>
-    <row r="45" spans="1:12" x14ac:dyDescent="0.45">
+      <c r="M44">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="45" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A45" s="2">
         <v>50</v>
       </c>
@@ -9691,37 +10036,40 @@
         <v>32</v>
       </c>
       <c r="C45" t="s">
+        <v>13</v>
+      </c>
+      <c r="D45" t="s">
         <v>28</v>
       </c>
-      <c r="D45" t="s">
-        <v>18</v>
-      </c>
-      <c r="E45">
+      <c r="E45" t="s">
+        <v>18</v>
+      </c>
+      <c r="F45">
         <v>88</v>
       </c>
-      <c r="F45">
+      <c r="G45">
         <v>77</v>
       </c>
-      <c r="G45">
+      <c r="H45">
         <v>70</v>
       </c>
-      <c r="H45">
-        <v>50</v>
-      </c>
       <c r="I45">
+        <v>50</v>
+      </c>
+      <c r="J45">
         <v>70</v>
       </c>
-      <c r="J45">
-        <v>20</v>
-      </c>
       <c r="K45">
-        <v>50</v>
+        <v>20</v>
       </c>
       <c r="L45">
+        <v>50</v>
+      </c>
+      <c r="M45">
         <v>66</v>
       </c>
     </row>
-    <row r="46" spans="1:12" x14ac:dyDescent="0.45">
+    <row r="46" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A46" s="2">
         <v>51</v>
       </c>
@@ -9732,34 +10080,37 @@
         <v>13</v>
       </c>
       <c r="D46" t="s">
-        <v>18</v>
-      </c>
-      <c r="E46">
+        <v>13</v>
+      </c>
+      <c r="E46" t="s">
+        <v>18</v>
+      </c>
+      <c r="F46">
         <v>30</v>
       </c>
-      <c r="F46">
-        <v>60</v>
-      </c>
       <c r="G46">
-        <v>50</v>
+        <v>60</v>
       </c>
       <c r="H46">
+        <v>50</v>
+      </c>
+      <c r="I46">
         <v>70</v>
       </c>
-      <c r="I46">
+      <c r="J46">
         <v>40</v>
       </c>
-      <c r="J46">
-        <v>20</v>
-      </c>
       <c r="K46">
+        <v>20</v>
+      </c>
+      <c r="L46">
         <v>10</v>
       </c>
-      <c r="L46">
+      <c r="M46">
         <v>40</v>
       </c>
     </row>
-    <row r="47" spans="1:12" x14ac:dyDescent="0.45">
+    <row r="47" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A47" s="2">
         <v>52</v>
       </c>
@@ -9767,37 +10118,40 @@
         <v>32</v>
       </c>
       <c r="C47" t="s">
+        <v>13</v>
+      </c>
+      <c r="D47" t="s">
         <v>28</v>
       </c>
-      <c r="D47" t="s">
-        <v>18</v>
-      </c>
-      <c r="E47">
-        <v>60</v>
+      <c r="E47" t="s">
+        <v>18</v>
       </c>
       <c r="F47">
+        <v>60</v>
+      </c>
+      <c r="G47">
         <v>10</v>
       </c>
-      <c r="G47">
-        <v>50</v>
-      </c>
       <c r="H47">
-        <v>30</v>
+        <v>50</v>
       </c>
       <c r="I47">
         <v>30</v>
       </c>
       <c r="J47">
+        <v>30</v>
+      </c>
+      <c r="K47">
         <v>40</v>
       </c>
-      <c r="K47">
-        <v>50</v>
-      </c>
       <c r="L47">
+        <v>50</v>
+      </c>
+      <c r="M47">
         <v>30</v>
       </c>
     </row>
-    <row r="48" spans="1:12" x14ac:dyDescent="0.45">
+    <row r="48" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A48" s="2">
         <v>53</v>
       </c>
@@ -9805,37 +10159,40 @@
         <v>32</v>
       </c>
       <c r="C48" t="s">
+        <v>13</v>
+      </c>
+      <c r="D48" t="s">
         <v>28</v>
       </c>
-      <c r="D48" t="s">
-        <v>18</v>
-      </c>
-      <c r="E48">
+      <c r="E48" t="s">
+        <v>18</v>
+      </c>
+      <c r="F48">
         <v>75</v>
       </c>
-      <c r="F48">
-        <v>20</v>
-      </c>
       <c r="G48">
-        <v>50</v>
+        <v>20</v>
       </c>
       <c r="H48">
+        <v>50</v>
+      </c>
+      <c r="I48">
         <v>10</v>
       </c>
-      <c r="I48">
-        <v>50</v>
-      </c>
       <c r="J48">
-        <v>1</v>
+        <v>50</v>
       </c>
       <c r="K48">
         <v>1</v>
       </c>
       <c r="L48">
+        <v>1</v>
+      </c>
+      <c r="M48">
         <v>75</v>
       </c>
     </row>
-    <row r="49" spans="1:12" x14ac:dyDescent="0.45">
+    <row r="49" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A49" s="2">
         <v>54</v>
       </c>
@@ -9843,37 +10200,40 @@
         <v>32</v>
       </c>
       <c r="C49" t="s">
+        <v>14</v>
+      </c>
+      <c r="D49" t="s">
         <v>28</v>
       </c>
-      <c r="D49" t="s">
-        <v>18</v>
-      </c>
-      <c r="E49">
+      <c r="E49" t="s">
+        <v>18</v>
+      </c>
+      <c r="F49">
         <v>80</v>
       </c>
-      <c r="F49">
+      <c r="G49">
         <v>40</v>
       </c>
-      <c r="G49">
+      <c r="H49">
         <v>100</v>
       </c>
-      <c r="H49">
-        <v>1</v>
-      </c>
       <c r="I49">
+        <v>1</v>
+      </c>
+      <c r="J49">
         <v>70</v>
       </c>
-      <c r="J49">
-        <v>1</v>
-      </c>
       <c r="K49">
         <v>1</v>
       </c>
       <c r="L49">
+        <v>1</v>
+      </c>
+      <c r="M49">
         <v>70</v>
       </c>
     </row>
-    <row r="50" spans="1:12" x14ac:dyDescent="0.45">
+    <row r="50" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A50" s="2">
         <v>55</v>
       </c>
@@ -9881,37 +10241,40 @@
         <v>32</v>
       </c>
       <c r="C50" t="s">
+        <v>14</v>
+      </c>
+      <c r="D50" t="s">
         <v>28</v>
       </c>
-      <c r="D50" t="s">
-        <v>18</v>
-      </c>
-      <c r="E50">
+      <c r="E50" t="s">
+        <v>18</v>
+      </c>
+      <c r="F50">
         <v>80</v>
       </c>
-      <c r="F50">
+      <c r="G50">
         <v>70</v>
       </c>
-      <c r="G50">
+      <c r="H50">
         <v>85</v>
       </c>
-      <c r="H50">
+      <c r="I50">
         <v>15</v>
       </c>
-      <c r="I50">
+      <c r="J50">
         <v>10</v>
       </c>
-      <c r="J50">
-        <v>20</v>
-      </c>
       <c r="K50">
-        <v>60</v>
+        <v>20</v>
       </c>
       <c r="L50">
+        <v>60</v>
+      </c>
+      <c r="M50">
         <v>70</v>
       </c>
     </row>
-    <row r="51" spans="1:12" x14ac:dyDescent="0.45">
+    <row r="51" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A51" s="2">
         <v>56</v>
       </c>
@@ -9919,37 +10282,40 @@
         <v>32</v>
       </c>
       <c r="C51" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="D51" t="s">
-        <v>18</v>
-      </c>
-      <c r="E51">
-        <v>60</v>
+        <v>13</v>
+      </c>
+      <c r="E51" t="s">
+        <v>18</v>
       </c>
       <c r="F51">
         <v>60</v>
       </c>
       <c r="G51">
+        <v>60</v>
+      </c>
+      <c r="H51">
         <v>80</v>
       </c>
-      <c r="H51">
-        <v>1</v>
-      </c>
       <c r="I51">
-        <v>50</v>
+        <v>1</v>
       </c>
       <c r="J51">
-        <v>1</v>
+        <v>50</v>
       </c>
       <c r="K51">
         <v>1</v>
       </c>
       <c r="L51">
+        <v>1</v>
+      </c>
+      <c r="M51">
         <v>80</v>
       </c>
     </row>
-    <row r="52" spans="1:12" x14ac:dyDescent="0.45">
+    <row r="52" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A52" s="2">
         <v>57</v>
       </c>
@@ -9957,37 +10323,40 @@
         <v>32</v>
       </c>
       <c r="C52" t="s">
+        <v>14</v>
+      </c>
+      <c r="D52" t="s">
         <v>28</v>
       </c>
-      <c r="D52" t="s">
-        <v>18</v>
-      </c>
-      <c r="E52">
+      <c r="E52" t="s">
+        <v>18</v>
+      </c>
+      <c r="F52">
         <v>90</v>
       </c>
-      <c r="F52">
+      <c r="G52">
         <v>15</v>
       </c>
-      <c r="G52">
+      <c r="H52">
         <v>70</v>
       </c>
-      <c r="H52">
+      <c r="I52">
         <v>55</v>
       </c>
-      <c r="I52">
+      <c r="J52">
         <v>40</v>
       </c>
-      <c r="J52">
+      <c r="K52">
         <v>70</v>
       </c>
-      <c r="K52">
+      <c r="L52">
         <v>52</v>
       </c>
-      <c r="L52">
+      <c r="M52">
         <v>65</v>
       </c>
     </row>
-    <row r="53" spans="1:12" x14ac:dyDescent="0.45">
+    <row r="53" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A53" s="2">
         <v>58</v>
       </c>
@@ -9995,37 +10364,40 @@
         <v>32</v>
       </c>
       <c r="C53" t="s">
+        <v>14</v>
+      </c>
+      <c r="D53" t="s">
         <v>28</v>
       </c>
-      <c r="D53" t="s">
-        <v>18</v>
-      </c>
-      <c r="E53">
+      <c r="E53" t="s">
+        <v>18</v>
+      </c>
+      <c r="F53">
         <v>80</v>
       </c>
-      <c r="F53">
-        <v>1</v>
-      </c>
       <c r="G53">
-        <v>60</v>
+        <v>1</v>
       </c>
       <c r="H53">
+        <v>60</v>
+      </c>
+      <c r="I53">
         <v>5</v>
       </c>
-      <c r="I53">
-        <v>1</v>
-      </c>
       <c r="J53">
+        <v>1</v>
+      </c>
+      <c r="K53">
         <v>10</v>
-      </c>
-      <c r="K53">
-        <v>70</v>
       </c>
       <c r="L53">
         <v>70</v>
       </c>
-    </row>
-    <row r="54" spans="1:12" x14ac:dyDescent="0.45">
+      <c r="M53">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="54" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A54" s="2">
         <v>59</v>
       </c>
@@ -10033,37 +10405,40 @@
         <v>32</v>
       </c>
       <c r="C54" t="s">
+        <v>14</v>
+      </c>
+      <c r="D54" t="s">
         <v>28</v>
       </c>
-      <c r="D54" t="s">
-        <v>18</v>
-      </c>
-      <c r="E54">
+      <c r="E54" t="s">
+        <v>18</v>
+      </c>
+      <c r="F54">
         <v>95</v>
       </c>
-      <c r="F54">
+      <c r="G54">
         <v>10</v>
       </c>
-      <c r="G54">
+      <c r="H54">
         <v>100</v>
       </c>
-      <c r="H54">
+      <c r="I54">
         <v>2</v>
       </c>
-      <c r="I54">
+      <c r="J54">
         <v>100</v>
       </c>
-      <c r="J54">
+      <c r="K54">
         <v>15</v>
       </c>
-      <c r="K54">
+      <c r="L54">
         <v>70</v>
       </c>
-      <c r="L54">
+      <c r="M54">
         <v>100</v>
       </c>
     </row>
-    <row r="55" spans="1:12" x14ac:dyDescent="0.45">
+    <row r="55" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A55" s="2">
         <v>60</v>
       </c>
@@ -10071,37 +10446,40 @@
         <v>32</v>
       </c>
       <c r="C55" t="s">
+        <v>14</v>
+      </c>
+      <c r="D55" t="s">
         <v>28</v>
       </c>
-      <c r="D55" t="s">
-        <v>18</v>
-      </c>
-      <c r="E55">
+      <c r="E55" t="s">
+        <v>18</v>
+      </c>
+      <c r="F55">
         <v>40</v>
       </c>
-      <c r="F55">
-        <v>1</v>
-      </c>
       <c r="G55">
+        <v>1</v>
+      </c>
+      <c r="H55">
         <v>80</v>
       </c>
-      <c r="H55">
-        <v>1</v>
-      </c>
       <c r="I55">
-        <v>20</v>
+        <v>1</v>
       </c>
       <c r="J55">
+        <v>20</v>
+      </c>
+      <c r="K55">
         <v>10</v>
       </c>
-      <c r="K55">
+      <c r="L55">
         <v>40</v>
       </c>
-      <c r="L55">
+      <c r="M55">
         <v>80</v>
       </c>
     </row>
-    <row r="56" spans="1:12" x14ac:dyDescent="0.45">
+    <row r="56" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A56" s="2">
         <v>61</v>
       </c>
@@ -10109,37 +10487,40 @@
         <v>32</v>
       </c>
       <c r="C56" t="s">
+        <v>14</v>
+      </c>
+      <c r="D56" t="s">
         <v>28</v>
       </c>
-      <c r="D56" t="s">
-        <v>18</v>
-      </c>
-      <c r="E56">
+      <c r="E56" t="s">
+        <v>18</v>
+      </c>
+      <c r="F56">
         <v>85</v>
       </c>
-      <c r="F56">
+      <c r="G56">
         <v>10</v>
       </c>
-      <c r="G56">
+      <c r="H56">
         <v>90</v>
       </c>
-      <c r="H56">
-        <v>1</v>
-      </c>
       <c r="I56">
+        <v>1</v>
+      </c>
+      <c r="J56">
         <v>90</v>
       </c>
-      <c r="J56">
-        <v>1</v>
-      </c>
       <c r="K56">
+        <v>1</v>
+      </c>
+      <c r="L56">
         <v>90</v>
       </c>
-      <c r="L56">
+      <c r="M56">
         <v>10</v>
       </c>
     </row>
-    <row r="57" spans="1:12" x14ac:dyDescent="0.45">
+    <row r="57" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A57" s="2">
         <v>62</v>
       </c>
@@ -10147,25 +10528,25 @@
         <v>32</v>
       </c>
       <c r="C57" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="D57" t="s">
-        <v>18</v>
-      </c>
-      <c r="E57">
-        <v>20</v>
+        <v>13</v>
+      </c>
+      <c r="E57" t="s">
+        <v>18</v>
       </c>
       <c r="F57">
-        <v>30</v>
+        <v>20</v>
       </c>
       <c r="G57">
         <v>30</v>
       </c>
       <c r="H57">
-        <v>60</v>
+        <v>30</v>
       </c>
       <c r="I57">
-        <v>20</v>
+        <v>60</v>
       </c>
       <c r="J57">
         <v>20</v>
@@ -10174,10 +10555,13 @@
         <v>20</v>
       </c>
       <c r="L57">
+        <v>20</v>
+      </c>
+      <c r="M57">
         <v>40</v>
       </c>
     </row>
-    <row r="58" spans="1:12" x14ac:dyDescent="0.45">
+    <row r="58" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A58" s="2">
         <v>63</v>
       </c>
@@ -10185,37 +10569,40 @@
         <v>32</v>
       </c>
       <c r="C58" t="s">
+        <v>14</v>
+      </c>
+      <c r="D58" t="s">
         <v>28</v>
       </c>
-      <c r="D58" t="s">
+      <c r="E58" t="s">
         <v>17</v>
       </c>
-      <c r="E58">
-        <v>60</v>
-      </c>
       <c r="F58">
         <v>60</v>
       </c>
       <c r="G58">
-        <v>50</v>
+        <v>60</v>
       </c>
       <c r="H58">
-        <v>20</v>
+        <v>50</v>
       </c>
       <c r="I58">
-        <v>60</v>
+        <v>20</v>
       </c>
       <c r="J58">
+        <v>60</v>
+      </c>
+      <c r="K58">
         <v>30</v>
-      </c>
-      <c r="K58">
-        <v>40</v>
       </c>
       <c r="L58">
         <v>40</v>
       </c>
-    </row>
-    <row r="59" spans="1:12" x14ac:dyDescent="0.45">
+      <c r="M58">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="59" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A59" s="2">
         <v>64</v>
       </c>
@@ -10223,37 +10610,40 @@
         <v>32</v>
       </c>
       <c r="C59" t="s">
+        <v>14</v>
+      </c>
+      <c r="D59" t="s">
         <v>28</v>
       </c>
-      <c r="D59" t="s">
-        <v>18</v>
-      </c>
-      <c r="E59">
+      <c r="E59" t="s">
+        <v>18</v>
+      </c>
+      <c r="F59">
         <v>30</v>
       </c>
-      <c r="F59">
+      <c r="G59">
         <v>40</v>
       </c>
-      <c r="G59">
-        <v>50</v>
-      </c>
       <c r="H59">
+        <v>50</v>
+      </c>
+      <c r="I59">
         <v>30</v>
       </c>
-      <c r="I59">
+      <c r="J59">
         <v>40</v>
       </c>
-      <c r="J59">
+      <c r="K59">
         <v>30</v>
       </c>
-      <c r="K59">
-        <v>20</v>
-      </c>
       <c r="L59">
         <v>20</v>
       </c>
-    </row>
-    <row r="60" spans="1:12" x14ac:dyDescent="0.45">
+      <c r="M59">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="60" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A60" s="2">
         <v>65</v>
       </c>
@@ -10261,37 +10651,40 @@
         <v>32</v>
       </c>
       <c r="C60" t="s">
+        <v>14</v>
+      </c>
+      <c r="D60" t="s">
         <v>28</v>
       </c>
-      <c r="D60" t="s">
-        <v>18</v>
-      </c>
-      <c r="E60">
+      <c r="E60" t="s">
+        <v>18</v>
+      </c>
+      <c r="F60">
         <v>90</v>
       </c>
-      <c r="F60">
-        <v>1</v>
-      </c>
       <c r="G60">
+        <v>1</v>
+      </c>
+      <c r="H60">
         <v>80</v>
       </c>
-      <c r="H60">
+      <c r="I60">
         <v>5</v>
       </c>
-      <c r="I60">
-        <v>50</v>
-      </c>
       <c r="J60">
+        <v>50</v>
+      </c>
+      <c r="K60">
         <v>25</v>
       </c>
-      <c r="K60">
-        <v>20</v>
-      </c>
       <c r="L60">
+        <v>20</v>
+      </c>
+      <c r="M60">
         <v>80</v>
       </c>
     </row>
-    <row r="61" spans="1:12" x14ac:dyDescent="0.45">
+    <row r="61" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A61" s="2">
         <v>66</v>
       </c>
@@ -10299,19 +10692,19 @@
         <v>32</v>
       </c>
       <c r="C61" t="s">
+        <v>14</v>
+      </c>
+      <c r="D61" t="s">
         <v>28</v>
       </c>
-      <c r="D61" t="s">
-        <v>18</v>
-      </c>
-      <c r="E61">
+      <c r="E61" t="s">
+        <v>18</v>
+      </c>
+      <c r="F61">
         <v>70</v>
       </c>
-      <c r="F61">
-        <v>20</v>
-      </c>
       <c r="G61">
-        <v>50</v>
+        <v>20</v>
       </c>
       <c r="H61">
         <v>50</v>
@@ -10320,16 +10713,19 @@
         <v>50</v>
       </c>
       <c r="J61">
-        <v>60</v>
+        <v>50</v>
       </c>
       <c r="K61">
         <v>60</v>
       </c>
       <c r="L61">
-        <v>50</v>
-      </c>
-    </row>
-    <row r="62" spans="1:12" x14ac:dyDescent="0.45">
+        <v>60</v>
+      </c>
+      <c r="M61">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="62" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A62" s="2">
         <v>67</v>
       </c>
@@ -10337,37 +10733,40 @@
         <v>32</v>
       </c>
       <c r="C62" t="s">
+        <v>14</v>
+      </c>
+      <c r="D62" t="s">
         <v>28</v>
       </c>
-      <c r="D62" t="s">
-        <v>18</v>
-      </c>
-      <c r="E62">
+      <c r="E62" t="s">
+        <v>18</v>
+      </c>
+      <c r="F62">
         <v>80</v>
       </c>
-      <c r="F62">
+      <c r="G62">
         <v>30</v>
       </c>
-      <c r="G62">
+      <c r="H62">
         <v>90</v>
       </c>
-      <c r="H62">
-        <v>1</v>
-      </c>
       <c r="I62">
-        <v>50</v>
+        <v>1</v>
       </c>
       <c r="J62">
-        <v>1</v>
+        <v>50</v>
       </c>
       <c r="K62">
         <v>1</v>
       </c>
       <c r="L62">
+        <v>1</v>
+      </c>
+      <c r="M62">
         <v>70</v>
       </c>
     </row>
-    <row r="63" spans="1:12" x14ac:dyDescent="0.45">
+    <row r="63" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A63" s="2">
         <v>68</v>
       </c>
@@ -10375,37 +10774,40 @@
         <v>32</v>
       </c>
       <c r="C63" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="D63" t="s">
-        <v>18</v>
-      </c>
-      <c r="E63">
+        <v>13</v>
+      </c>
+      <c r="E63" t="s">
+        <v>18</v>
+      </c>
+      <c r="F63">
         <v>30</v>
       </c>
-      <c r="F63">
+      <c r="G63">
         <v>40</v>
       </c>
-      <c r="G63">
-        <v>50</v>
-      </c>
       <c r="H63">
-        <v>40</v>
+        <v>50</v>
       </c>
       <c r="I63">
         <v>40</v>
       </c>
       <c r="J63">
-        <v>2</v>
+        <v>40</v>
       </c>
       <c r="K63">
         <v>2</v>
       </c>
       <c r="L63">
+        <v>2</v>
+      </c>
+      <c r="M63">
         <v>70</v>
       </c>
     </row>
-    <row r="64" spans="1:12" x14ac:dyDescent="0.45">
+    <row r="64" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A64" s="2">
         <v>69</v>
       </c>
@@ -10413,37 +10815,40 @@
         <v>32</v>
       </c>
       <c r="C64" t="s">
+        <v>14</v>
+      </c>
+      <c r="D64" t="s">
         <v>28</v>
       </c>
-      <c r="D64" t="s">
-        <v>18</v>
-      </c>
-      <c r="E64">
+      <c r="E64" t="s">
+        <v>18</v>
+      </c>
+      <c r="F64">
         <v>80</v>
       </c>
-      <c r="F64">
+      <c r="G64">
         <v>10</v>
       </c>
-      <c r="G64">
+      <c r="H64">
         <v>90</v>
       </c>
-      <c r="H64">
-        <v>1</v>
-      </c>
       <c r="I64">
-        <v>20</v>
+        <v>1</v>
       </c>
       <c r="J64">
         <v>20</v>
       </c>
       <c r="K64">
+        <v>20</v>
+      </c>
+      <c r="L64">
         <v>10</v>
       </c>
-      <c r="L64">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="65" spans="1:12" x14ac:dyDescent="0.45">
+      <c r="M64">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="65" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A65" s="2">
         <v>70</v>
       </c>
@@ -10451,37 +10856,40 @@
         <v>32</v>
       </c>
       <c r="C65" t="s">
+        <v>14</v>
+      </c>
+      <c r="D65" t="s">
         <v>28</v>
       </c>
-      <c r="D65" t="s">
-        <v>18</v>
-      </c>
-      <c r="E65">
-        <v>50</v>
+      <c r="E65" t="s">
+        <v>18</v>
       </c>
       <c r="F65">
+        <v>50</v>
+      </c>
+      <c r="G65">
         <v>30</v>
       </c>
-      <c r="G65">
+      <c r="H65">
         <v>80</v>
-      </c>
-      <c r="H65">
-        <v>30</v>
       </c>
       <c r="I65">
         <v>30</v>
       </c>
       <c r="J65">
-        <v>40</v>
+        <v>30</v>
       </c>
       <c r="K65">
         <v>40</v>
       </c>
       <c r="L65">
+        <v>40</v>
+      </c>
+      <c r="M65">
         <v>70</v>
       </c>
     </row>
-    <row r="66" spans="1:12" x14ac:dyDescent="0.45">
+    <row r="66" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A66" s="2">
         <v>71</v>
       </c>
@@ -10489,37 +10897,40 @@
         <v>32</v>
       </c>
       <c r="C66" t="s">
+        <v>14</v>
+      </c>
+      <c r="D66" t="s">
         <v>28</v>
       </c>
-      <c r="D66" t="s">
-        <v>18</v>
-      </c>
-      <c r="E66">
+      <c r="E66" t="s">
+        <v>18</v>
+      </c>
+      <c r="F66">
         <v>88</v>
       </c>
-      <c r="F66">
+      <c r="G66">
         <v>5</v>
       </c>
-      <c r="G66">
+      <c r="H66">
         <v>86</v>
       </c>
-      <c r="H66">
+      <c r="I66">
         <v>6</v>
       </c>
-      <c r="I66">
+      <c r="J66">
         <v>62</v>
       </c>
-      <c r="J66">
+      <c r="K66">
         <v>12</v>
       </c>
-      <c r="K66">
+      <c r="L66">
         <v>10</v>
       </c>
-      <c r="L66">
+      <c r="M66">
         <v>88</v>
       </c>
     </row>
-    <row r="67" spans="1:12" x14ac:dyDescent="0.45">
+    <row r="67" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A67" s="2">
         <v>72</v>
       </c>
@@ -10527,38 +10938,41 @@
         <v>32</v>
       </c>
       <c r="C67" t="s">
+        <v>14</v>
+      </c>
+      <c r="D67" t="s">
         <v>28</v>
       </c>
-      <c r="D67" t="s">
-        <v>18</v>
-      </c>
-      <c r="E67">
+      <c r="E67" t="s">
+        <v>18</v>
+      </c>
+      <c r="F67">
         <v>75</v>
       </c>
-      <c r="F67">
+      <c r="G67">
         <v>35</v>
       </c>
-      <c r="G67">
+      <c r="H67">
         <v>40</v>
       </c>
-      <c r="H67">
+      <c r="I67">
         <v>75</v>
       </c>
-      <c r="I67">
+      <c r="J67">
         <v>35</v>
-      </c>
-      <c r="J67">
-        <v>75</v>
       </c>
       <c r="K67">
         <v>75</v>
       </c>
       <c r="L67">
+        <v>75</v>
+      </c>
+      <c r="M67">
         <v>40</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:L67" xr:uid="{9D83972C-8AA1-494E-8B24-51FD46390AC9}"/>
+  <autoFilter ref="A1:M67" xr:uid="{9D83972C-8AA1-494E-8B24-51FD46390AC9}"/>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -10567,15 +10981,15 @@
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{71FF9DBE-7E0B-40C8-BA3F-EE2D0D8F897A}">
   <dimension ref="A1:E5"/>
-  <sheetFormatPr defaultRowHeight="14" x14ac:dyDescent="0.45"/>
+  <sheetFormatPr defaultRowHeight="13.9" x14ac:dyDescent="0.4"/>
   <cols>
-    <col min="2" max="2" width="12.87890625" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="6.41015625" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="6.234375" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="3.41015625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="12.86328125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="6.3984375" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="6.19921875" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="3.3984375" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="1" spans="1:5" x14ac:dyDescent="0.4">
       <c r="A1" s="1" t="s">
         <v>33</v>
       </c>
@@ -10592,7 +11006,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="2" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="2" spans="1:5" x14ac:dyDescent="0.4">
       <c r="A2" t="s">
         <v>44</v>
       </c>
@@ -10609,7 +11023,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="3" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="3" spans="1:5" x14ac:dyDescent="0.4">
       <c r="A3" t="s">
         <v>45</v>
       </c>
@@ -10626,7 +11040,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="4" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="4" spans="1:5" x14ac:dyDescent="0.4">
       <c r="A4" t="s">
         <v>44</v>
       </c>
@@ -10643,7 +11057,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="5" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="5" spans="1:5" x14ac:dyDescent="0.4">
       <c r="A5" t="s">
         <v>45</v>
       </c>
@@ -10669,16 +11083,16 @@
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{479708D6-69A4-45A0-8682-2B2B736D6623}">
   <dimension ref="A1:E15"/>
-  <sheetFormatPr defaultRowHeight="14" x14ac:dyDescent="0.45"/>
+  <sheetFormatPr defaultRowHeight="13.9" x14ac:dyDescent="0.4"/>
   <cols>
-    <col min="1" max="1" width="9.87890625" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="12.87890625" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="6.41015625" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="6.234375" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="3.41015625" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="9.86328125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="12.86328125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="6.3984375" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="6.19921875" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="3.3984375" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="1" spans="1:5" x14ac:dyDescent="0.4">
       <c r="A1" s="1" t="s">
         <v>39</v>
       </c>
@@ -10695,7 +11109,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="2" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="2" spans="1:5" x14ac:dyDescent="0.4">
       <c r="A2" t="s">
         <v>21</v>
       </c>
@@ -10712,7 +11126,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="3" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="3" spans="1:5" x14ac:dyDescent="0.4">
       <c r="A3" t="s">
         <v>21</v>
       </c>
@@ -10729,7 +11143,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="4" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="4" spans="1:5" x14ac:dyDescent="0.4">
       <c r="A4" t="s">
         <v>22</v>
       </c>
@@ -10746,7 +11160,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="5" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="5" spans="1:5" x14ac:dyDescent="0.4">
       <c r="A5" t="s">
         <v>22</v>
       </c>
@@ -10763,7 +11177,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="6" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="6" spans="1:5" x14ac:dyDescent="0.4">
       <c r="A6" t="s">
         <v>40</v>
       </c>
@@ -10780,7 +11194,7 @@
         <v>52</v>
       </c>
     </row>
-    <row r="7" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="7" spans="1:5" x14ac:dyDescent="0.4">
       <c r="A7" t="s">
         <v>40</v>
       </c>
@@ -10797,7 +11211,7 @@
         <v>52</v>
       </c>
     </row>
-    <row r="8" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="8" spans="1:5" x14ac:dyDescent="0.4">
       <c r="A8" t="s">
         <v>41</v>
       </c>
@@ -10814,7 +11228,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="9" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="9" spans="1:5" x14ac:dyDescent="0.4">
       <c r="A9" t="s">
         <v>41</v>
       </c>
@@ -10831,7 +11245,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="10" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="10" spans="1:5" x14ac:dyDescent="0.4">
       <c r="A10" t="s">
         <v>42</v>
       </c>
@@ -10848,7 +11262,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="11" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="11" spans="1:5" x14ac:dyDescent="0.4">
       <c r="A11" t="s">
         <v>42</v>
       </c>
@@ -10865,7 +11279,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="12" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="12" spans="1:5" x14ac:dyDescent="0.4">
       <c r="A12" t="s">
         <v>25</v>
       </c>
@@ -10882,7 +11296,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="13" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="13" spans="1:5" x14ac:dyDescent="0.4">
       <c r="A13" t="s">
         <v>25</v>
       </c>
@@ -10899,7 +11313,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="14" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="14" spans="1:5" x14ac:dyDescent="0.4">
       <c r="A14" t="s">
         <v>43</v>
       </c>
@@ -10916,7 +11330,7 @@
         <v>52</v>
       </c>
     </row>
-    <row r="15" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="15" spans="1:5" x14ac:dyDescent="0.4">
       <c r="A15" t="s">
         <v>43</v>
       </c>
